--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7387,7 +7387,11 @@
           <t>「傘忘れたでしょう！」弟に喝を入れた長女。よく気づいたね、と感動したのも束の間でした</t>
         </is>
       </c>
-      <c r="C162" s="23" t="n"/>
+      <c r="C162" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/14T09:07:14+09:00</t>
+        </is>
+      </c>
       <c r="D162" s="22" t="inlineStr">
         <is>
           <t>2029/04/28</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7597,7 +7597,75 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="15.75" customHeight="1" s="18"/>
+    <row r="165" ht="15.75" customHeight="1" s="18">
+      <c r="A165" s="23" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="23" t="inlineStr">
+        <is>
+          <t>「これにレリッシュとブラックペッパー合わせたら絶対美味しいんじゃない？」小6長男が大人の舌すぎる件</t>
+        </is>
+      </c>
+      <c r="C165" s="23" t="n"/>
+      <c r="D165" s="22" t="inlineStr">
+        <is>
+          <t>2029/05/19</t>
+        </is>
+      </c>
+      <c r="E165" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F165" s="23" t="inlineStr">
+        <is>
+          <t>小6長男の舌が、完全に大人だった件🧀
+昨日は仕事がお休み。
+夕飯はちょっとした晩酌です🍷
+ままかり、ポークチャーシュー、キムチ、蒸し野菜。
+子どもたちとワイワイ食事。
+長男は小さいときから
+美味しいものが分かるタイプ。
+大人が好きな味も普通に食べられます。
+今回買ってきたのは
+「ベームスタースプリングミルク」
+春の若草を食べた牛のミルクで作る
+期間限定のオランダのチーズです。
+クラッカーにのせて食べてみると
+クリーミーで美味しい。
+でも正直、少しパンチが欲しいな…
+と思っていたところに、長男が一言。
+「お母さん、これにレリッシュと
+　ブラックペッパー合わせたら
+　絶対美味しいんじゃない？」
+…衝撃😳
+レリッシュは刻んだピクルス。
+甘酸っぱい味です。
+ヒントは私の食べ方でした。
+その日の私は
+ままかり＋レリッシュ＋クラッカー。
+それを見て
+「レリッシュはチーズにも合うんじゃ？」
+そこにブラックペッパーを足したのは
+長男のオリジナル。
+これは試すでしょう。
+…絶対美味しい！！
+レリッシュの甘み
+ブラックペッパーの香り
+そしてチーズの美味しさ。
+抜群に合うんです✨
+でも驚いたのは味よりも
+食べたことのない組み合わせを
+食べる前に「絶対美味しい」と
+想像できた長男のほう。
+小6の舌、恐るべし。
+次は何を提案してくるのか楽しみです😂
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学6年生 #チーズ #おうちごはん #晩酌 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="166" ht="15.75" customHeight="1" s="18"/>
     <row r="167" ht="15.75" customHeight="1" s="18"/>
     <row r="168" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7460,7 +7460,11 @@
           <t>「5時に起こして」宿題が終わらなかった日、小1次男が自分で決めた翌朝</t>
         </is>
       </c>
-      <c r="C163" s="23" t="n"/>
+      <c r="C163" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/17T09:06:06+09:00</t>
+        </is>
+      </c>
       <c r="D163" s="22" t="inlineStr">
         <is>
           <t>2029/05/05</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7670,7 +7670,65 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="15.75" customHeight="1" s="18"/>
+    <row r="166" ht="15.75" customHeight="1" s="18">
+      <c r="A166" s="23" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="23" t="inlineStr">
+        <is>
+          <t>収納のために買った2段ベッド。ベッド下が子どもたちのヌックと化して、収納ケースが追加できません</t>
+        </is>
+      </c>
+      <c r="C166" s="23" t="n"/>
+      <c r="D166" s="22" t="inlineStr">
+        <is>
+          <t>2029/05/26</t>
+        </is>
+      </c>
+      <c r="E166" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F166" s="23" t="inlineStr">
+        <is>
+          <t>最近、2段ベッドを買いました🛏
+決め手は、1段目のベッドの位置が高いこと。
+ベッド下が大容量の収納スペースになるんです。
+ここに子どもたちの洋服を全部しまえば
+衣替えの手間がだいぶ省ける✨
+ベッドと一緒に収納ケースも購入。
+ただ、前のベッドがまだ家にあったので
+とりあえず4つだけ。
+残りはあとで追加すればいいや…
+この「あとで」が命取りでした。
+ベッド下は、あっという間に
+子どもたちの秘密基地に😇
+①家の中でサバゲーをやるときの攻撃拠点
+　そこから相手を攻撃する
+②怒られたときの隠れ場所
+③こっそりぬいぐるみと遊ぶ高学年
+　（誰とは言いません）
+結論。
+追加の収納ケースを購入できません。泣
+あんなに狭くて暗いところの
+どこがいいのか、私には分かりません。
+でもこんな小さなスペースでも
+子どもたちの想像力次第で
+攻撃する場所にも、隠れる場所にもなる。
+今では子どもたちが大好きな場所です。
+子どもたちにとっては
+「ヌック」的な心地よい居場所に
+なっているのかもしれません🏠
+収納ケースを追加したい母と
+ヌックを守りたい子どもたち。
+今のところ、子どもたちの圧勝です。泣
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #2段ベッド #ニトリ #子ども部屋 #収納 #秘密基地 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="167" ht="15.75" customHeight="1" s="18"/>
     <row r="168" ht="15.75" customHeight="1" s="18"/>
     <row r="169" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F167"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7729,7 +7729,99 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="15.75" customHeight="1" s="18"/>
+    <row r="167" ht="15.75" customHeight="1" s="18">
+      <c r="A167" s="23" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="23" t="inlineStr">
+        <is>
+          <t>パソコンを壊した小4長女と、アクシデントレポートを書いてみた。吊し上げないための振り返り</t>
+        </is>
+      </c>
+      <c r="C167" s="23" t="n"/>
+      <c r="D167" s="22" t="inlineStr">
+        <is>
+          <t>2029/06/02</t>
+        </is>
+      </c>
+      <c r="E167" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F167" s="23" t="inlineStr">
+        <is>
+          <t>長女(小4)がパパのパソコンを壊しました💻
+玄関に靴が出しっぱなし。
+パソコンでゲームをしていた長女に
+「靴を片付けて」と声をかけました。
+だいたい一度では動きません。
+何度か言って、ようやく重たい腰を上げて
+玄関へ向かっていきました。
+その直後——
+「ガンっ！」
+バツの悪そうな顔で戻ってきて
+「落としちゃった」
+画面は黒いまま。
+たぶん修理が必要な状態です😢
+片手にパソコンを持ったまま
+何かをしようとしてはいけない。
+落として壊す可能性があるから。
+再三、伝えてきたことでした。
+それでもやっぱり事故は起きました。
+子どもの不注意で修理に出すのは2回目。
+パパは怒りきれません。
+でも冷静に考えると
+今回は長女がトリガーになっただけで
+子どもたちの使い方を見ていると
+誰もが同じ状況になる可能性はありました。
+だとしたら長女を責めて終わるのは
+いちばん意味がない。
+そこで、アクシデントレポートを
+書いてもらうことにしました📝
+・起きてしまった事実を書く
+・原因を考える
+・対策を考えて振り返る
+長女が書いたのがこちら。
+【げんいん】
+・くつをかたずけなかった
+・かたてでもっていた
+【おきたこと】
+ゲームをしていて、くつをかたずけろと
+言われたので、パソコンをもちながら
+（かたてで）いってしまった。
+なのでおとしてしまった。
+【かいぜんほうほう】
+・さいしょにくつをかたずけておく
+・かたてでもたない
+・どこかに行く時はおいておく
+・立ちながらもたない
+しっかり考えられていました✨
+特にいいのは、4つとも
+「自分が次にできる行動」になっていること。
+「気をつける」で終わっていません。
+しかも1つ目が
+「さいしょにくつをかたずけておく」。
+落とした場面だけでなく
+その前の段階まで戻っているんです。
+長女には、はっきり伝えました。
+これは吊し上げじゃない。
+みんなで気をつけていこうという話で
+自分にも当てはまることはなかったか
+それぞれが振り返るチャンスだよ、と。
+失敗したときこそ改善できるチャンス。
+そして大事なのはタイミング。
+記憶は時間が経つと曖昧になるので
+新しいうちに、その日のうちに。
+これで何か変わるかは分かりません。
+でも叱って終わりにしていたら
+残るのは「怒られた」記憶だけでした。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学4年生 #子育て日記 #失敗から学ぶ #振り返り #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="168" ht="15.75" customHeight="1" s="18"/>
     <row r="169" ht="15.75" customHeight="1" s="18"/>
     <row r="170" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7738,7 +7738,11 @@
           <t>パソコンを壊した小4長女と、アクシデントレポートを書いてみた。吊し上げないための振り返り</t>
         </is>
       </c>
-      <c r="C167" s="23" t="n"/>
+      <c r="C167" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/18T20:53:35+09:00</t>
+        </is>
+      </c>
       <c r="D167" s="22" t="inlineStr">
         <is>
           <t>2029/06/02</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7543,7 +7543,11 @@
           <t>アイスベストは入浴介助で雲泥の差。訪問看護師が1年使ってわかったこと</t>
         </is>
       </c>
-      <c r="C164" s="23" t="n"/>
+      <c r="C164" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/19T09:06:07+09:00</t>
+        </is>
+      </c>
       <c r="D164" s="22" t="inlineStr">
         <is>
           <t>2029/05/12</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -1471,7 +1471,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C91" s="19" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/09/21T09:06:28+09:00</t>
         </is>
       </c>
       <c r="D91" s="0" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F167"/>
+  <dimension ref="A1:F168"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7830,7 +7830,66 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="15.75" customHeight="1" s="18"/>
+    <row r="168" ht="15.75" customHeight="1" s="18">
+      <c r="A168" s="23" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="23" t="inlineStr">
+        <is>
+          <t>「男性ならヤクルトダンディかな？」小6長男のネーミングセンスに吹き出した話</t>
+        </is>
+      </c>
+      <c r="C168" s="23" t="n"/>
+      <c r="D168" s="22" t="inlineStr">
+        <is>
+          <t>2029/06/09</t>
+        </is>
+      </c>
+      <c r="E168" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F168" s="23" t="inlineStr">
+        <is>
+          <t>長男とテレビを見ていたら
+ヤクルトレディの特集をやっていました📺
+ふと思い出したのが、育休中のこと。
+子どもと散歩していたら
+ヤクルトレディのお姉さんが声をかけてくれて
+「今お仕事されていないようであれば
+　子育てしながら働けるヤクルトレディに
+　興味はありませんか？」
+ただ子どもと歩いていただけなのに
+まさかの勧誘😳 初めての体験でした。
+そんな思い出話を長男にしていたら
+長男が一言。
+「女性はヤクルトレディって言うんでしょ？
+　じゃあ、男性ならヤクルトダンディかな？」
+……ヤクルトダンディ！？😂
+末尾の「ディ」を合わせてきた！
+レディ、ダンディ。
+思わず吹き出しました。
+でも確かに気になる。
+男性ならなんて言うんだろう？
+そもそも女性以外は働けるの？
+調べてみたら
+男性も働いていて、全国に約400人。
+（ヤクルトレディは3万2000人以上）
+男性だけの決まった呼び名は
+ないそうです。
+つまりヤクルトダンディは
+残念ながら非公式。
+でも公式の呼び名がないなら
+ヤクルトダンディでいいのでは…？
+ヤクルトダンディ、ぜひ見てみたいです。
+小6男子のネーミングセンス、侮れません。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学6年生 #子どもの名言 #ヤクルトレディ #クスッと笑える #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="169" ht="15.75" customHeight="1" s="18"/>
     <row r="170" ht="15.75" customHeight="1" s="18"/>
     <row r="171" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7890,7 +7890,67 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="15.75" customHeight="1" s="18"/>
+    <row r="169" ht="15.75" customHeight="1" s="18">
+      <c r="A169" s="23" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="23" t="inlineStr">
+        <is>
+          <t>「邪悪な波動に染まりし呼び込み君」で車内が爆笑。名古屋までの道中は呼び込み君アレンジの聴き比べでした</t>
+        </is>
+      </c>
+      <c r="C169" s="23" t="n"/>
+      <c r="D169" s="22" t="inlineStr">
+        <is>
+          <t>2029/06/16</t>
+        </is>
+      </c>
+      <c r="E169" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F169" s="23" t="inlineStr">
+        <is>
+          <t>スーパーに入ると聞こえてくる
+おなじみのあのメロディ。
+「呼び込み君」🎵
+先日、家族で名古屋へ行った道中のこと。
+車の中では子どもたちが聴きたい音楽をかけて
+楽しく向かっていました🚗
+長女「呼び込み君、聞きたい」
+…スーパーのあれです。
+リクエストどおりにかけて
+下にスクロールしていくと
+こんなタイトルが。
+「邪悪な波動に染まりし呼び込み君」
+…邪悪な波動に、染まりし。
+これはかけるしかありません😂
+始まりは、気持ちおしゃれな
+いつもの呼び込み君のメロディ。
+と思ったのも束の間——
+突然始まる、壮大な邪悪モード！！
+呼び込み君ってこんな感じだったか？
+まるで違う雰囲気なのに
+ちゃんと呼び込み君のメロディが入っていて
+吹き出してしまいました。
+スケールはどんどん大きくなり
+最後はなんと「蛍の光」で締め。
+・おしゃれな始まり → 開店
+・壮大な邪悪モード → タイムセール
+・蛍の光 → 閉店
+スーパーの1日が1曲で完結していました👏
+呼び込み君のアレンジって
+YouTubeに結構あるんですね。
+色々な呼び込み君を聞きながら
+名古屋に着きました。
+とても面白かったです🎶
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #家族旅行 #名古屋 #車内BGM #呼び込み君 #クスッと笑える #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="170" ht="15.75" customHeight="1" s="18"/>
     <row r="171" ht="15.75" customHeight="1" s="18"/>
     <row r="172" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F169"/>
+  <dimension ref="A1:F170"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -7951,7 +7951,68 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="15.75" customHeight="1" s="18"/>
+    <row r="170" ht="15.75" customHeight="1" s="18">
+      <c r="A170" s="23" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="23" t="inlineStr">
+        <is>
+          <t>「お母さんだからできるんだよ」家族でカエル逆立ちに挑戦したら、何十年ぶりの母が15秒キープで優勝した日</t>
+        </is>
+      </c>
+      <c r="C170" s="23" t="n"/>
+      <c r="D170" s="22" t="inlineStr">
+        <is>
+          <t>2029/06/23</t>
+        </is>
+      </c>
+      <c r="E170" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F170" s="23" t="inlineStr">
+        <is>
+          <t>長男が「アンテナ」という技を
+見せてくれた流れから
+「カエル逆立ちってできる？」という話に🐸
+さっそく子どもたちが挑戦！
+長男 → できず
+長女 → できず
+次男 → 数秒できた！
+驚いたことに、できたのは小1の次男だけ。
+続いて夫が挑戦。
+大人の意地を見せるかと思いきや…
+1〜2秒。
+そして私。
+なんとなく「私できそう」と思い
+バランスをとりながら足をふわっとあげると——
+できるではありませんか！！
+何十年ぶりのカエル逆立ち。
+まさかの成功、しかも15秒くらいキープ✨
+母、優勝です🏆
+それを見た長男
+「お母さんだからできるんだよ
+　俺にはできない」
+…と言いつつ
+寝室で一人で練習していました😂
+ちょこっとできるようになって嬉しそう。
+次男はやればやるほど上達。
+長女は端から諦めて、やろうともせず。
+同じことでも3人の反応がバラバラ。
+きょうだいって面白いです。
+そのうち子どもたちはカエル逆立ちに飽き
+始まったのが「新・横揺れ界隈」の
+ダンスバトル💃
+謎の横揺れダンスに爆笑。
+体操教室からのダンスホールと化した
+我が家でした🎶
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #カエル逆立ち #きょうだい #おうち時間 #クスッと笑える #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="171" ht="15.75" customHeight="1" s="18"/>
     <row r="172" ht="15.75" customHeight="1" s="18"/>
     <row r="173" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -4190,7 +4190,7 @@
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>2026/06/20</t>
+          <t>2026/09/23T09:07:32+09:00</t>
         </is>
       </c>
       <c r="D94" s="0" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F170"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8013,7 +8013,85 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="15.75" customHeight="1" s="18"/>
+    <row r="171" ht="15.75" customHeight="1" s="18">
+      <c r="A171" s="23" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="23" t="inlineStr">
+        <is>
+          <t>Excelもプログラミングも分からない訪問看護師が、AIで事務作業を減らした話</t>
+        </is>
+      </c>
+      <c r="C171" s="23" t="n"/>
+      <c r="D171" s="22" t="inlineStr">
+        <is>
+          <t>2029/06/30</t>
+        </is>
+      </c>
+      <c r="E171" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F171" s="23" t="inlineStr">
+        <is>
+          <t>訪問看護の事務作業を
+AIに手伝ってもらっています🩺💻
+いちばん大きかった変化。
+事務さんが半日くらいかけて作っていた
+月間の訪問スケジュールが
+数分で終わるようになりました。
+こう言うと
+「ITに詳しいんですね」と
+思われるかもしれませんが、違います。
+私がExcelでできるのは
+足し算と平均を出すことくらい。
+関数もほとんど分かりません。
+始まりは、自分のためではなく
+事務さんでした。
+毎月必ず来る仕事で、時間もかかる。
+毎月ストレスを感じているのが
+見ていて分かったんです。
+やったのは
+「困っていることをそのまま話す」だけ。
+専門用語は使っていません。使えません。
+同僚に説明するのと同じ言葉で話したら
+AIが形にしてくれました。
+詳しくないほうが
+向いているかもしれません。
+「こう作るべき」という正解を
+持っていないので
+困っていることをそのまま言うしかない。
+実はそれがいちばん大事な情報でした。
+【看護師がAIを使うときに守ること】
+・何をどこまで扱うかは個人で判断しない
+・先に職場でルールを決めて
+　上司の了解を得てから
+・使うサービスが情報をどう扱うか確認する
+私も上司の了解を得てから始めました。
+ここは個人の裁量でやる部分ではありません。
+【うまくいかなかったこと】
+ある管理表をExcelで作ったのですが
+現場では今までの紙の運用に
+足していく形のほうが簡単でした。
+新しい仕組みに全部移すのではなく
+現場に合わせて引くことも改善のうち。
+今は月間スケジュールから広がって
+訪問実績や件数、週間スケジュールまで。
+1〜2か所で完結する仕組みを作っています。
+事務が減れば、訪問に時間が回せる。
+私は訪問そのものが好きなので✨
+「詳しくないから無理」と
+諦めている方がいたら
+そこは入口ではないとお伝えしたいです。
+困っていることは
+もう十分に分かっているはずですから。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#訪問看護 #訪問看護師 #看護師 #業務改善 #AI活用 #看護師ママ #ワーキングマザー #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="172" ht="15.75" customHeight="1" s="18"/>
     <row r="173" ht="15.75" customHeight="1" s="18"/>
     <row r="174" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7614,7 +7614,11 @@
           <t>「これにレリッシュとブラックペッパー合わせたら絶対美味しいんじゃない？」小6長男が大人の舌すぎる件</t>
         </is>
       </c>
-      <c r="C165" s="23" t="n"/>
+      <c r="C165" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/25T09:06:26+09:00</t>
+        </is>
+      </c>
       <c r="D165" s="22" t="inlineStr">
         <is>
           <t>2029/05/19</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F171"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8096,7 +8096,81 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="15.75" customHeight="1" s="18"/>
+    <row r="172" ht="15.75" customHeight="1" s="18">
+      <c r="A172" s="23" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="23" t="inlineStr">
+        <is>
+          <t>楽天モバイルを3年使った正直な話。1回線8,000円が2,000円台になったけれど、困ることもあります</t>
+        </is>
+      </c>
+      <c r="C172" s="23" t="n"/>
+      <c r="D172" s="22" t="inlineStr">
+        <is>
+          <t>2029/07/07</t>
+        </is>
+      </c>
+      <c r="E172" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F172" s="23" t="inlineStr">
+        <is>
+          <t>楽天モバイルを3年使った正直な話📱
+ソフトバンクから乗り換えて3年。
+【料金】
+1回線あたり 月8,000円くらい
+　↓
+2,000〜3,000円に
+夫婦2回線なので月およそ1万円、
+年間だと10万円以上変わりました。
+でも、いいことばかりではありません。
+【弱いのはこの3つ】
+・地下
+・ビルの中
+・山間部
+3年経っても、ここは変わっていません。
+そして、いちばん困るのがこれ。
+電波の入らないお店では
+・スマホ決済が使えない
+・ポイントが出せない
+・クーポンが表示できない
+私は現金を持ち歩かないので
+支払いはクレジットカードに切り替えます。
+でもポイントやクーポンは諦めることに😢
+対策らしい対策はしていません。
+電波が弱いときは、諦めています。
+【これはすごくいい】
+Rakuten Linkという通話アプリ。
+相手がLINEを使っていなくても
+普通の電話番号にかけて無料なんです☎️
+学校、病院、お店、実家。
+LINEでつながっていない相手にかける機会は
+意外と多いので、かなり助かっています。
+【外回りの仕事では困っていません】
+訪問看護で1日中外にいますが
+仕事中に電波で困ったことはありません。
+弱いのは屋内なので
+外を動き回る人には向いていると思います。
+【向かない人】
+ビルの中や地下にいる時間が長い人。
+安さ以上にストレスが大きいはずです。
+ちなみに長男(小6)は日本通信。
+外で使うことがほとんどなく
+自宅や友達の家のWi-Fiだけで足りるので
+いちばん安いところにしました。
+親と同じ会社にする必要はありません。
+安さだけで決めると、レジの前で困ります。
+どこで困るかを先に知ったうえで
+選ぶのがいちばんだと思います😊
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#楽天モバイル #格安SIM #通信費 #節約 #3人育児 #ワーキングマザー #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="173" ht="15.75" customHeight="1" s="18"/>
     <row r="174" ht="15.75" customHeight="1" s="18"/>
     <row r="175" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7687,7 +7687,11 @@
           <t>収納のために買った2段ベッド。ベッド下が子どもたちのヌックと化して、収納ケースが追加できません</t>
         </is>
       </c>
-      <c r="C166" s="23" t="n"/>
+      <c r="C166" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/26T09:08:05+09:00</t>
+        </is>
+      </c>
       <c r="D166" s="22" t="inlineStr">
         <is>
           <t>2029/05/26</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F172"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8175,7 +8175,83 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="15.75" customHeight="1" s="18"/>
+    <row r="173" ht="15.75" customHeight="1" s="18">
+      <c r="A173" s="23" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="23" t="inlineStr">
+        <is>
+          <t>スマホが圏外で決済できない。地下のお店でクーポンが出せなかった日と、それからやっていること</t>
+        </is>
+      </c>
+      <c r="C173" s="23" t="n"/>
+      <c r="D173" s="22" t="inlineStr">
+        <is>
+          <t>2029/07/14</t>
+        </is>
+      </c>
+      <c r="E173" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F173" s="23" t="inlineStr">
+        <is>
+          <t>お店で圏外になって
+決済できなかった話です📱
+その日は地下にある飲食店で食事。
+そのお店には専用アプリがあって
+中にクーポンが入っています。
+出かける前、自宅でクーポンを確認。
+ちゃんとある。これを使おう。
+——ここが落とし穴でした。
+家では電波があるのでアプリは開きます。
+だから「準備できた」と思い込んでいました。
+席について、食事をして
+そのあいだ、電波がないことには
+気づいていませんでした。
+そして、いざお会計。
+このお店は席で決済ができる仕組みなので
+スマホを開くと——
+電波がない😱
+・クーポンが出てこない
+・席での決済もできない
+さっきまで当たり前に使えていたものが
+全部止まります。
+助かったのは、財布のクレジットカード。
+私は普段、現金をほとんど持ちません。
+でもカードは常に入れています。
+カードは通信がなくても使えるので
+支払いそのものには困りませんでした。
+ただ、クーポンは使えず。
+大きな損ではないけれど
+ちょっと残念な気持ちに…😢
+【それからやっていること】
+お店に入った時点で
+電波が入るかを確認する。
+これだけです。
+画面をちらっと見るだけ。
+電波が入っていなければ
+・クーポンは最初から諦める
+・支払いはカードでいくと決めておく
+先に分かっていれば、会計で慌てません。
+「入る前」ではなく「入った時点で」。
+家で見ても意味がなかったので💦
+よく「いざというときのために
+現金を持ち歩きましょう」と言われます。
+それも正解のひとつ。
+でも現金を持たない生活をしている人には
+別の答えがあると思っています。
+・通信がなくても使える手段を1つ持つ
+・その場で使えるかを確かめる
+現金に戻るのではなく
+圏外でも詰まない形を用意しておく✨
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#キャッシュレス #スマホ決済 #圏外 #クレジットカード #暮らしの工夫 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="174" ht="15.75" customHeight="1" s="18"/>
     <row r="175" ht="15.75" customHeight="1" s="18"/>
     <row r="176" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8252,7 +8252,96 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="15.75" customHeight="1" s="18"/>
+    <row r="174" ht="15.75" customHeight="1" s="18">
+      <c r="A174" s="23" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="23" t="inlineStr">
+        <is>
+          <t>「もう！スクイーズ触らせないからね！！」誕生日にスクイーズ20個を手にした長女が、スクイーズ屋さんを開店しました</t>
+        </is>
+      </c>
+      <c r="C174" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/26T16:32:42+09:00</t>
+        </is>
+      </c>
+      <c r="D174" s="22" t="inlineStr">
+        <is>
+          <t>2029/07/21</t>
+        </is>
+      </c>
+      <c r="E174" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F174" s="23" t="inlineStr">
+        <is>
+          <t>長女の誕生日は9月28日🎂
+でも今日、念願のスクイーズをゲットしました！
+今日31のアイスケーキを買ってきたら
+「アイスケーキを食べながら
+　プレゼントをもらいたい」と本人の希望。
+しかも土曜日で家族もそろっている。
+…なるほど。というわけで2日前倒しです。
+この日をずっと待っていた長女。
+毎日「楽しみ、楽しみ」とワクワク。
+ひとつ取り出すたびに
+「わーっ！」
+「きゃー！かわいい！！」
+ハイテンションが止まりません😂
+正直に言います。
+長女がそこまで熱狂するスクイーズ、
+私にはその魅力が1mmも分かりません。泣
+でも本人がこれだけ喜んでいるので
+それでいいのだと思います。
+プレゼントのスクイーズは全部で20個。
+そして長女には前から
+言っていたことがありました。
+「スクイーズをもらったら
+　スクイーズ屋さんをやる！」
+というわけで早速、開店🏪
+面白いのは
+長男(小6)と次男(小1)も参加したこと。
+小6男子まで巻き込むスクイーズ、恐るべし。
+でも楽しそうだったのも束の間。
+長女の気に入らない扱いをする兄弟には
+指導が入ります。
+「もう！スクイーズ触らせないからね！！」
+…出ました。謎のスクイーズマウント。
+お店をやっているはずなのに
+商品に触らせない店主です😂
+そのあとも喧嘩が勃発したり
+長女の指導が入ったり、まあ賑やか。
+そのうち
+「お母さん！きてー！」
+とお呼びがかかり、私もお客さんに。
+商品を手に取って驚いたこと。
+バターのスクイーズは
+バターの匂いがするんです🧈
+見た目だけでなく匂いまで作り込んである。
+なかなか手がこんでいました。
+「物を買うのではなく
+　欲しいものを買ってもらえる経験を買う」
+夫と話して決めたことでしたが
+今日の長女を見ていて
+それでよかったと思っています。
+ちなみに我が家のこの週末は
+・今日(26日土)アイスケーキとスクイーズ
+・明日(27日日)長女希望でスタミナ太郎
+・28日(月・当日)特に予定なし
+当日がいちばん平凡という
+なんとも言えないスケジュールですが
+長女にとっては3日間まるごとが
+バースデイズなんだと思います😊
+長女、誕生日おめでとう🎉
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学4年生 #誕生日 #スクイーズ #きょうだい #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="175" ht="15.75" customHeight="1" s="18"/>
     <row r="176" ht="15.75" customHeight="1" s="18"/>
     <row r="177" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8329,7 +8329,7 @@
 それでよかったと思っています。
 ちなみに我が家のこの週末は
 ・今日(26日土)アイスケーキとスクイーズ
-・明日(27日日)長女希望でスタミナ太郎
+・明日(27日日)長女希望ですたみな太郎
 ・28日(月・当日)特に予定なし
 当日がいちばん平凡という
 なんとも言えないスケジュールですが

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -4580,7 +4580,7 @@
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/09/28T09:14:30+09:00</t>
         </is>
       </c>
       <c r="D104" s="0" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F174"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8342,7 +8342,80 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="15.75" customHeight="1" s="18"/>
+    <row r="175" ht="15.75" customHeight="1" s="18">
+      <c r="A175" s="23" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="23" t="inlineStr">
+        <is>
+          <t>「起きたら一番におめでとうって声かけて」長女の誕生日。パパのおめでとうは、なかったことになりました</t>
+        </is>
+      </c>
+      <c r="C175" s="23" t="inlineStr">
+        <is>
+          <t>2026/09/28T12:26:54+09:00</t>
+        </is>
+      </c>
+      <c r="D175" s="22" t="inlineStr">
+        <is>
+          <t>2029/07/28</t>
+        </is>
+      </c>
+      <c r="E175" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F175" s="23" t="inlineStr">
+        <is>
+          <t>今日は長女の誕生日🎂本番の日です。
+前日の夜、寝る前に長女から一言。
+「起きたら一番におめでとうって声かけて」
+…なるほど。一番に、がポイントらしい。
+そして当日の朝。
+リビングに入ってきた長女に
+「お誕生日おめでとう！」と声をかけると
+満面の笑みで「ありがとう！！」
+嬉しそうな顔に
+こっちまで幸せな気持ちになりました😊
+さて、ここからが本題です。
+私と長女がそんなやりとりをしている合間に
+夫も「おめでとう」と声をかけていました。
+ちゃんと言っていたんです。私は聞いています。
+でも——長女は反応せず。
+そして朝食中。
+長女「パパからのおめでとうがない」
+夫「朝起きてきたときに言ったよ」
+長女「聞こえなかった」
+…なかったことになりました😂
+夫は常日頃、長女に奴隷のように
+扱われているので、長女からすると
+「自分への祝福がないなんて信じられない」
+という感覚なのだと思います。
+いや、あったんですけどね。
+ついでに長女の夫への評価。
+・メガネが嫌い
+・メガネを外しても変
+・全然かっこよくない
+どうしろと😇
+かけても外してもダメって逃げ場がない。
+そんな扱いを受けながらも
+夫は朝いちばんに声をかけていました。
+聞いてもらえなかったけれど。
+ドンマイ、夫。
+あなたの愛はきっと長女に届いているはず。
+ちなみに当の本人は
+理不尽な不満を言われても
+無視をされても全く気にしていません。
+これはこれで、すごいと思います。
+長女、誕生日おめでとう🎉
+そして夫、お疲れさまです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学4年生 #誕生日 #パパ #クスッと笑える #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="176" ht="15.75" customHeight="1" s="18"/>
     <row r="177" ht="15.75" customHeight="1" s="18"/>
     <row r="178" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8409,7 +8409,7 @@
 無視をされても全く気にしていません。
 これはこれで、すごいと思います。
 長女、誕生日おめでとう🎉
-そして夫、お疲れさまです。
+パパのおめでとうも、ちゃんとありましたよ。
 ▶️ 続きはプロフィールのブログへ！
 https://3nin-dotabata.com
 #3人育児 #小学生ママ #小学4年生 #誕生日 #パパ #クスッと笑える #ドタバタ母さん</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/09/30T09:07:03+09:00</t>
         </is>
       </c>
       <c r="D68" s="0" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F176"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8416,7 +8416,87 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="15.75" customHeight="1" s="18"/>
+    <row r="176" ht="15.75" customHeight="1" s="18">
+      <c r="A176" s="23" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="23" t="inlineStr">
+        <is>
+          <t>小1は20時、小4は20時半、小6は21時。平均より1時間以上早い我が家の寝る時間と、続けて変わったこと</t>
+        </is>
+      </c>
+      <c r="C176" s="23" t="n"/>
+      <c r="D176" s="22" t="inlineStr">
+        <is>
+          <t>2029/08/04</t>
+        </is>
+      </c>
+      <c r="E176" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F176" s="23" t="inlineStr">
+        <is>
+          <t>我が家の子どもの寝る時間💤
+・小1(次男)　20時
+・小4(長女)　20時30分
+・小6(長男)　21時
+学年が上がるごとに30分ずつ。
+調べてみたら
+小学生の平均就寝時刻は21時37分。
+つまり我が家は
+どの学年も平均より1時間以上早いんです。
+理由はひとつ。
+必要な睡眠時間を確保するため。
+いちばん変化があったのは長女。
+朝がまったく起きられない子でしたが
+この生活リズムを続けて
+近頃ようやく6時に起きられるように✨
+「ようやく」です。
+何か月もかけて、少しずつでした。
+次男は20時が就寝時間ですが
+正直、厳密には20時15分ごろ。
+寝る前に音読と読書をしているからです。
+寝ている間に記憶が定着すると聞いて
+実践しています📖
+長男は朝5時半には起きてしまいます。
+夜が整うと、朝は勝手に整う。
+そして我が家が続けている
+いちばん現実的な理由。
+遅くまで起きていても
+ゲームとYouTubeの時間が増えるだけ。
+宿題が進むわけでも
+家族の会話が増えるわけでもない。
+だったら寝たほうがいい。
+我が家の軸は
+「頭も体も心も休ませることが優先」
+よく寝て、日中しっかり活動して
+しっかり食べる。
+書いてみると本当に当たり前のこと。
+でもその当たり前が
+当たり前でない時代でもあります。
+正直に言うと、続けるのは大変です😢
+毎日「寝る時間だよー」と言い続けて
+それでもなかなか寝室に行かない。泣
+日によってはストレスも溜まります。
+きれいに回っているわけではなく
+それでも続けているだけです。
+【思いがけない効果】
+私も21時就寝・5時起きになりました。
+そうしたら風邪をひかなくなり
+心身ともに元気になった気がします😊
+子どものためにやっていたことで
+自分のほうが健康になっていました。
+遠回りのようで
+いちばんの近道なのかもしれません。
+今日も「寝る時間だよー」と言い続けます。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #早寝早起き #生活リズム #子どもの睡眠 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="177" ht="15.75" customHeight="1" s="18"/>
     <row r="178" ht="15.75" customHeight="1" s="18"/>
     <row r="179" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8447,8 +8447,25 @@
 小学生の平均就寝時刻は21時37分。
 つまり我が家は
 どの学年も平均より1時間以上早いんです。
-理由はひとつ。
-必要な睡眠時間を確保するため。
+いちばん大きな理由はこれ。
+我が家は小学校まで歩いて30分以上。
+朝は7時20分までに家を出ないと
+間に合いません🏃
+逆算すると6時前後には起きていないと
+回らないんです。
+そこに「必要な睡眠時間10〜11時間」を
+足すと、自然にこの時間になりました。
+この習慣は長男のときから続いていて
+下の2人はそれに倣っただけ。
+3人目はいちばんラクでした😊
+【続けて気づいたこと】
+同じ時間に寝るようにすると
+ベッドに入ってからがすごく早い。
+子どもたちは数分で寝てしまいます。
+条件反射のように、みんな静かな寝息。
+「なかなか寝ない」のではなく
+「寝る時間が毎日違う」から
+寝ないのかもしれません。
 いちばん変化があったのは長女。
 朝がまったく起きられない子でしたが
 この生活リズムを続けて

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F177"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8514,7 +8514,76 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="15.75" customHeight="1" s="18"/>
+    <row r="177" ht="15.75" customHeight="1" s="18">
+      <c r="A177" s="23" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="23" t="inlineStr">
+        <is>
+          <t>毎晩数分の音読を2か月続けたら、驚くほど上手になりました。おまけに字まで</t>
+        </is>
+      </c>
+      <c r="C177" s="23" t="n"/>
+      <c r="D177" s="22" t="inlineStr">
+        <is>
+          <t>2029/08/11</t>
+        </is>
+      </c>
+      <c r="E177" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F177" s="23" t="inlineStr">
+        <is>
+          <t>小1次男と毎晩続けている音読📖
+8月の中旬に始めて2か月。
+その報告です。
+結論から言うと——
+音読が驚くほど上手になりました✨
+特別なことは何もしていません。
+毎晩数分、続けただけです。
+【変化】
+始めたころ、教材に出てくる
+短歌や俳句が難しそうで
+一言ずつ区切るような読み方でした。
+・最初：一言ずつ区切って読む
+・しばらくして：何度か繰り返すと
+　スムーズに読めるときが増える
+・今：まとまりのある言葉ですらすら
+繰り返さなくても
+最初から読めるようになりました。
+そして予想していなかった変化がもう1つ。
+字を書くのも上手になったんです🖊
+音読しかしていないのに
+書くほうまで変わりました。
+読むことと書くことは
+どこかでつながっているのかも。
+【やっていること】
+・毎晩、数分の音読
+・好きな本の読み聞かせ
+以上です。
+続けられた理由があるとすれば
+長くやろうとしなかったこと。
+数分だから毎日できます。
+30分やろうとしていたら
+たぶん1週間で終わっていました。
+【宿題が終わらない日も削りません】
+本人がこの時間を楽しみにしているし
+積み上げてきた習慣を
+1日分の宿題と引き換えにしたくないから。
+1日休むと、次の日も休みやすくなるので。
+数分の音読は地味です。
+その日のうちには何も変わりません。
+でも2か月で変わりました。
+気がついたら上手になっていた、
+という感じです😊
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学1年生 #音読 #家庭学習 #習慣化 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="178" ht="15.75" customHeight="1" s="18"/>
     <row r="179" ht="15.75" customHeight="1" s="18"/>
     <row r="180" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F177"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8584,7 +8584,79 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="15.75" customHeight="1" s="18"/>
+    <row r="178" ht="15.75" customHeight="1" s="18">
+      <c r="A178" s="23" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="23" t="inlineStr">
+        <is>
+          <t>「どうして俺たちのはないの？」長女に、と思ってもらったカチカチキーホルダーが、結局3人で分けることになった話</t>
+        </is>
+      </c>
+      <c r="C178" s="23" t="n"/>
+      <c r="D178" s="22" t="inlineStr">
+        <is>
+          <t>2029/08/18</t>
+        </is>
+      </c>
+      <c r="E178" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F178" s="23" t="inlineStr">
+        <is>
+          <t>カチカチキーホルダーをもらいました🔑
+ハンドメイドが好きな職場の方から
+いま流行っているというキーホルダーを
+いただきました。
+「失敗作なんですけど」と言われましたが
+…どこが失敗しているのか分かりません。
+ちゃんとカチカチするし、かわいいし
+仕上がりもきれい。
+作る人の目ってすごいです。
+「何個でもどうぞ」とのお言葉に甘えて
+6個いただきました。
+・長女が喜びそう
+・長女の仲のいい友達にもあげられるかも
+そう思って、つい多めに😊
+いただいたものがなかなか凝っていて
+・鉢植えからクマが出ているもの
+　（頭を押すと隠れる）
+・キーボードのカチカチする感触のもの
+・押すと光るタイプ
+…これで失敗作。
+帰宅後、長女に見せると
+「可愛い！！」と弾ける笑顔✨
+きらきらした表情でとっても嬉しそう。
+喜んでくれてよかったぁ。
+…と安心していたのも束の間。
+「どうして俺たちのはないの？」
+長男と次男からの不満です。
+いやいや、これ完全に女子の好きなものでしょ。
+しかも言い出したのは長男(小6)でした。
+長男発信の不満に次男が乗った流れ😂
+小6男子が、カチカチキーホルダー。
+そこからは
+「私がもらったんだから」
+「お前ばっかりずるい」
+と喧嘩が勃発しそうに。
+結局、兄弟3人で仲良く分けることに。
+長女の友達に、という話はどこかへ…
+分けたあとは驚くほど平和でした。
+それぞれ満足げな表情で
+お互いのカチカチを貸し借りし合っています。
+喧嘩しないで遊べるじゃないか！
+ツッコみたくなった日でした。
+自分のぶんさえあれば、あとは仲良くできる。
+3人きょうだいの揉めごとの9割は
+たぶんここなんだと思います。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #きょうだい #ハンドメイド #クスッと笑える #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="179" ht="15.75" customHeight="1" s="18"/>
     <row r="180" ht="15.75" customHeight="1" s="18"/>
     <row r="181" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7847,7 +7847,11 @@
           <t>「男性ならヤクルトダンディかな？」小6長男のネーミングセンスに吹き出した話</t>
         </is>
       </c>
-      <c r="C168" s="23" t="n"/>
+      <c r="C168" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/02T09:06:01+09:00</t>
+        </is>
+      </c>
       <c r="D168" s="22" t="inlineStr">
         <is>
           <t>2029/06/09</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7911,7 +7911,11 @@
           <t>「邪悪な波動に染まりし呼び込み君」で車内が爆笑。名古屋までの道中は呼び込み君アレンジの聴き比べでした</t>
         </is>
       </c>
-      <c r="C169" s="23" t="n"/>
+      <c r="C169" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/03T09:05:07+09:00</t>
+        </is>
+      </c>
       <c r="D169" s="22" t="inlineStr">
         <is>
           <t>2029/06/16</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/10/05T09:07:36+09:00</t>
         </is>
       </c>
       <c r="D69" s="0" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>2026/06/03</t>
+          <t>2026/10/07T09:05:13+09:00</t>
         </is>
       </c>
       <c r="D70" s="0" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F179"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8665,7 +8665,94 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="15.75" customHeight="1" s="18"/>
+    <row r="179" ht="15.75" customHeight="1" s="18">
+      <c r="A179" s="23" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="23" t="inlineStr">
+        <is>
+          <t>保護者面談を3人分。事前に質問メモを作っていったら、短い時間でも聞きたいことが聞けました</t>
+        </is>
+      </c>
+      <c r="C179" s="23" t="n"/>
+      <c r="D179" s="22" t="inlineStr">
+        <is>
+          <t>2029/08/25</t>
+        </is>
+      </c>
+      <c r="E179" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F179" s="23" t="inlineStr">
+        <is>
+          <t>保護者面談がありました。3人分📝
+小1、小4、小6。
+学年も気になることも全部違います。
+面談でいちばん困るのが時間の短さ。
+「何かご質問は」と言われたときには
+もう残り数分…
+聞きたかったことを聞けないまま終わる。
+何度もやりました😢
+そこで今回は
+学年ごとに質問メモシートを作って臨みました。
+・0 今日いちばん聞きたいこと（◎○△）
+・1 学校での様子（メモ欄）
+・2 相談したいこと（質問文をそのまま書く）
+・3 家での取り組み
+・4 先生へのお願い
+・5 振り返り（面談後に記入）
+意外だったのは
+面談そのものより
+作っている時間に価値があったこと。
+書き出すうちに
+自分が何を心配しているのかがはっきりします。
+もやっとしたまま行くと話が散らかるけれど
+紙に書くと、本当に聞きたいことは2〜3つでした。
+【効いた工夫】
+①優先順位を◎○△でつけておく
+②冒頭で「今日は◯つ伺いたいことがあります」
+　と伝える（先生が時間配分してくれる）
+③質問文を「〜でしょうか？」まで書いておく
+④最後に「今日は◯◯していただける
+　ということでよろしいですか」と確認
+⑤お願いは「そろえたい」の形にする
+そして肝心の中身。
+3人とも、全部違いました。
+褒めてもらえたところも
+これからのところも、見事にバラバラ。
+同じ親から生まれて、同じ家で
+同じようなリズムで育っているのに。
+当たり前なのですが
+一人の人間なんだなぁとしみじみ。
+【思わぬ発見】
+我が家ではホワイトボードに
+「帰宅後にやることリスト」を作っています。
+もともとは小1の次男のために作ったもの。
+ところが——小6の長男も見ていました。
+「小さい子向けだから上の子には要らない」
+と思っていたけれど違いました。
+見える形になっているほうが
+学年に関係なく動きやすい。
+先生にお伝えしたら
+「視覚からのアプローチのほうが
+効果があるかもしれませんね」と共有できました。
+家でやっていることは
+面談で積極的に伝えたほうがいいです✨
+【面談を終えて決めたこと】
+①それぞれの強みが活かせるようサポート
+②探究心は育てていきたい
+③失敗を恐れずチャレンジできる環境を作る
+④怒りすぎないようにしたい
+…4つ目がいちばん難しい😅
+一緒に成長できたらいいなと思っています。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #保護者面談 #個人面談 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="180" ht="15.75" customHeight="1" s="18"/>
     <row r="181" ht="15.75" customHeight="1" s="18"/>
     <row r="182" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8718,6 +8718,18 @@
 ④最後に「今日は◯◯していただける
 　ということでよろしいですか」と確認
 ⑤お願いは「そろえたい」の形にする
+【これがいちばん効いたかも】
+気持ちが強く入っている話題ほど
+紙に書いていったほうがいいです。
+どうしても伝えたいことがあると
+つい感情が先に出てしまう。
+でも事前に書いておくと
+当日は読み上げるだけでいい。
+感情が先に出そうになっても紙に戻れます。
+おかげで今回は
+感情任せのクレーマーにならずに済みました。笑
+伝えたいことはちゃんと伝わって
+でも冷静でいられました✨
 そして肝心の中身。
 3人とも、全部違いました。
 褒めてもらえたところも

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8726,8 +8726,9 @@
 でも事前に書いておくと
 当日は読み上げるだけでいい。
 感情が先に出そうになっても紙に戻れます。
-おかげで今回は
-感情任せのクレーマーにならずに済みました。笑
+言いたいことが強い面談だったので
+熱くなったら嫌だなと思っていました。
+でも大丈夫でした。紙に戻れたからです。
 伝えたいことはちゃんと伝わって
 でも冷静でいられました✨
 そして肝心の中身。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8766,7 +8766,97 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="15.75" customHeight="1" s="18"/>
+    <row r="180" ht="15.75" customHeight="1" s="18">
+      <c r="A180" s="23" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="23" t="inlineStr">
+        <is>
+          <t>「姿勢よく食べよう」と言い続けても直らなかった次男。椅子を変えたら、その日から一度も膝を立てませんでした</t>
+        </is>
+      </c>
+      <c r="C180" s="23" t="n"/>
+      <c r="D180" s="22" t="inlineStr">
+        <is>
+          <t>2029/09/01</t>
+        </is>
+      </c>
+      <c r="E180" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F180" s="23" t="inlineStr">
+        <is>
+          <t>次男(小1)の姿勢の話です。
+食事中、気がつくとすぐに立て膝。
+・日頃の習慣はどこでも出てしまうよ
+・気持ちよく食べられるように気をつけよう
+・姿勢よく食べたほうが食事もおいしいよ
+何度も声をかけてきました。
+伝え方も変えてみました。
+それでも、なかなか直らない。
+毎食言って、毎食直らない😢
+正直、次男の問題だと思っていました。
+落ち着きがないのかな、意識が足りないのかな。
+我が家では食事はダイニングソファ。
+大人には何の問題もない椅子です。
+でも次男にとっては——
+・足の裏をつけるには浅く座るしかない
+・奥まで座って背もたれを使うと足が浮く
+足をつけると背もたれが使えず
+背もたれを使うと足が浮く。
+姿勢に「遊び」ができてしまうんです。
+そして、ここがいちばん情けなかったところ。
+私は訪問看護師です。
+現場では、椅子に座っていただくとき
+必ず足の裏が床についているかを見ます。
+足が浮くと体が安定せず姿勢が崩れる。
+だから高さを調整したり足台を置いたり。
+座面の奥行きが体に合っているかも見ます。
+基本中の基本。毎日やっていること。
+それを自分の家ではまったく見ていませんでした。
+【やったこと】
+ダイニングのお誕生日席に
+足の裏がしっかり床につく
+小さめの椅子を置きました🪑
+使ったのは中に物を収納できる
+四角い箱型のスツール。
+・次男の体にサイズぴったり
+・座面が小さいので深く座っても足がつく
+・中に物をしまえるので場所も無駄にならない
+我が家は昇降テーブルなので
+机の高さも次男に合わせられました。
+【結果】
+その日、一度も膝を立てずに
+食事ができました✨
+一度もです。
+あれだけ毎食言っていたのに。
+途中で席を立つことはあります。
+でも座っているあいだの姿勢は別物でした。
+そして何より
+「姿勢！」と何度も言う必要がなくなりました。
+環境を変えるだけでこんなに変わるのか。
+同時に、申し訳ない気持ちにもなりました。
+次男のせいにしていましたが
+悪かったのは環境でした。
+意識でも性格でもなく
+足が安定していなかっただけ。
+言っても直らないことは
+本人の問題ではないかもしれません。
+・足の裏は床についているか
+・座面の奥行きは体に合っているか
+・机の高さは合っているか
+大人のサイズで作られた家の中では
+子どもだけがずっと無理をしているのかも。
+毎食声をかけているなら
+一度、足元を見てみてください👀
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #小学1年生 #姿勢 #子どもの姿勢 #訪問看護師 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="181" ht="15.75" customHeight="1" s="18"/>
     <row r="182" ht="15.75" customHeight="1" s="18"/>
     <row r="183" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7976,7 +7976,11 @@
           <t>「お母さんだからできるんだよ」家族でカエル逆立ちに挑戦したら、何十年ぶりの母が15秒キープで優勝した日</t>
         </is>
       </c>
-      <c r="C170" s="23" t="n"/>
+      <c r="C170" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/09T09:07:31+09:00</t>
+        </is>
+      </c>
       <c r="D170" s="22" t="inlineStr">
         <is>
           <t>2029/06/23</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F180"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8861,7 +8861,89 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="15.75" customHeight="1" s="18"/>
+    <row r="181" ht="15.75" customHeight="1" s="18">
+      <c r="A181" s="23" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="23" t="inlineStr">
+        <is>
+          <t>大掃除ではなく「小掃除」。朝7時から1時間半で和室が終わったら、1日が驚くほど充実しました</t>
+        </is>
+      </c>
+      <c r="C181" s="23" t="n"/>
+      <c r="D181" s="22" t="inlineStr">
+        <is>
+          <t>2029/09/08</t>
+        </is>
+      </c>
+      <c r="E181" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F181" s="23" t="inlineStr">
+        <is>
+          <t>10月に入ったので
+我が家は大掃除を始めました🧹
+早いと思われるかもしれませんが
+理由が3つあります。
+①年末に余裕を持って過ごせる
+②粗大ゴミを出すチャンスがまだ何度もある
+③窓拭きを寒い中でやりたくない
+特に②と③は切実。
+年末に片付け始めても
+粗大ゴミの回収日が間に合わないんです。
+【我が家のやり方】
+一度に全部はやりません。
+セクションに分けて1か所ずつ。
+1か所に集中して午前中に終わらせる。
+「大掃除」ではなく「小掃除」という感覚です。
+【今日やったこと：和室】
+・ベッド下の整理整頓と掃除機がけ
+・棚の整理整頓
+・寝具の圧縮袋が壊れていたので入れ替え
+・押し入れの整理
+ゴミ袋1つ分の不用品を手放せました。
+朝7時スタート、1時間半で終了。
+想定は2時間だったので30分早く終わりました。
+余った時間でリビングの長男用棚も整理。
+こちらは15分で終了。
+【そのあとの午前中】
+・靴を4足洗った
+・食料品と日用品の買い物
+・なんなら40分の背中の筋トレまで
+【午後】
+・胃カメラの予約
+・使っていない口座の解約
+どちらも急がないけど
+やらなきゃいけないこと。
+つい後回しになるやつです。
+それが今日、片付きました✨
+今日いちばんの発見は
+掃除そのものではありませんでした。
+1か所を早く終わらせると
+そのあとの1日が連鎖的に動き出す。
+・想定より早く終わる
+・「まだ時間がある」という余力が生まれる
+・ついでにもう1か所やる
+・後回しにしていたことに手が伸びる
+最初の1時間半が、1日全部を変えました。
+朝から「今日は大掃除の日」と決めて
+家中をやっていたら
+夕方にはくたくただったと思います。
+【小掃除をすすめたい理由】
+・終わりが見える（1か所・2時間）
+・1日が潰れない（午後が丸ごと残る）
+・体力のあるうちにできる
+・早く終わればおまけがついてくる
+今日はビールが美味しいです🍺
+次はキッチンです。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#大掃除 #小掃除 #片付け #暮らしの工夫 #年末準備 #3人育児 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="182" ht="15.75" customHeight="1" s="18"/>
     <row r="183" ht="15.75" customHeight="1" s="18"/>
     <row r="184" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8919,6 +8919,27 @@
 やらなきゃいけないこと。
 つい後回しになるやつです。
 それが今日、片付きました✨
+【ただし、ひと波乱】
+口座の解約に行ったら
+銀行印がなかったんです😱
+出かけるときに確認したのに。
+家を出てからバッグは一度も開けていないのに。
+銀行の床も探してない。
+一旦帰宅して自宅を捜索…やっぱりない。
+この印鑑、ほかの口座の届出印でもあるので
+紛失したら本当に困る。
+銀行に連絡して待っていたら電話が。
+「こちらにありました」
+神様ありがとう🙏
+袋からキャッシュカードを出すときに
+一緒にポロリと落ちたようです。
+この1件で1時間のロス💦
+【そして思わぬおまけ】
+無事に解約できたのですが
+使っていない口座に埋蔵金がありました✨
+昨今、個人情報の流出もニュースに溢れています。
+使っていない口座は解約しておくのがいい、
+と実感しました（埋蔵金のこともあり笑）
 今日いちばんの発見は
 掃除そのものではありませんでした。
 1か所を早く終わらせると

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -8919,44 +8919,11 @@
 やらなきゃいけないこと。
 つい後回しになるやつです。
 それが今日、片付きました✨
-【ただし、ひと波乱】
-口座の解約に行ったら
-銀行印がなかったんです😱
-出かけるときに確認したのに。
-家を出てからバッグは一度も開けていないのに。
-銀行の床も探してない。
-一旦帰宅して自宅を捜索…やっぱりない。
-この印鑑、ほかの口座の届出印でもあるので
-紛失したら本当に困る。
-銀行に連絡して待っていたら電話が。
-「こちらにありました」
-神様ありがとう🙏
-袋からキャッシュカードを出すときに
-一緒にポロリと落ちたようです。
-この1件で1時間のロス💦
-【そして思わぬおまけ】
-無事に解約できたのですが
-使っていない口座に埋蔵金がありました✨
-昨今、個人情報の流出もニュースに溢れています。
-使っていない口座は解約しておくのがいい、
-と実感しました（埋蔵金のこともあり笑）
 今日いちばんの発見は
 掃除そのものではありませんでした。
 1か所を早く終わらせると
 そのあとの1日が連鎖的に動き出す。
-・想定より早く終わる
-・「まだ時間がある」という余力が生まれる
-・ついでにもう1か所やる
-・後回しにしていたことに手が伸びる
 最初の1時間半が、1日全部を変えました。
-朝から「今日は大掃除の日」と決めて
-家中をやっていたら
-夕方にはくたくただったと思います。
-【小掃除をすすめたい理由】
-・終わりが見える（1か所・2時間）
-・1日が潰れない（午後が丸ごと残る）
-・体力のあるうちにできる
-・早く終わればおまけがついてくる
 今日はビールが美味しいです🍺
 次はキッチンです。
 ▶️ 続きはプロフィールのブログへ！
@@ -8965,7 +8932,76 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="15.75" customHeight="1" s="18"/>
+    <row r="182" ht="15.75" customHeight="1" s="18">
+      <c r="A182" s="23" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="23" t="inlineStr">
+        <is>
+          <t>使っていない口座を解約したら、銀行印を紛失しかけて、最後に埋蔵金が出てきた話</t>
+        </is>
+      </c>
+      <c r="C182" s="23" t="n"/>
+      <c r="D182" s="22" t="inlineStr">
+        <is>
+          <t>2029/09/15</t>
+        </is>
+      </c>
+      <c r="E182" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F182" s="23" t="inlineStr">
+        <is>
+          <t>使っていない銀行口座を解約してきました🏦
+ずっと後回しにしていたこと。
+「急がないけど、やらなきゃいけないこと」です。
+ところが、すんなりいきませんでした。
+窓口で通帳を出して、印鑑を出そうとして——
+ない。
+え、ない😱
+出かけるときにしっかり確認したんです。
+家を出てからバッグは一度も開けていない。
+なんで？？
+銀行の床も探しましたがありません。
+一旦引き上げて、自宅を捜索。
+やっぱりない。
+銀行に落とし物の確認の連絡を入れて
+待つあいだも行動範囲をくまなく捜索。
+この印鑑、ほかの口座の届出印でもあるんです。
+紛失したら本当に困る…
+そのとき、銀行から電話が。
+祈る思いで出ると——
+「こちらにありました」
+神様ありがとう🙏
+袋からキャッシュカードを出すときに
+一緒にポロリと落ちたようです。
+我が家は紛失しないように
+印鑑と通帳をいつも一緒に保管しています。
+一緒にしているからこそ
+出すときに一緒に落ちたわけで…
+この1件で1時間のロスでした💦
+【そして思わぬおまけ】
+無事に解約できたのですが
+使っていない口座に埋蔵金がありました✨
+完全に忘れていたお金です。
+【使っていない口座は解約したほうがいい】
+①個人情報の流出がニュースに溢れる昨今
+　使っていない口座をそのままにするのは
+　管理していない窓口を開けっぱなしに
+　しているようなもの
+②埋蔵金が見つかることがあります（笑）
+持ち物は通帳・届出印・キャッシュカード・
+本人確認書類（銀行により違うので要確認）
+そして窓口で出すときは
+印鑑が一緒に落ちていないか確認を。本当に。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#銀行口座 #解約 #お金の管理 #暮らしの工夫 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="183" ht="15.75" customHeight="1" s="18"/>
     <row r="184" ht="15.75" customHeight="1" s="18"/>
     <row r="185" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8042,7 +8042,11 @@
           <t>Excelもプログラミングも分からない訪問看護師が、AIで事務作業を減らした話</t>
         </is>
       </c>
-      <c r="C171" s="23" t="n"/>
+      <c r="C171" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/10T09:07:25+09:00</t>
+        </is>
+      </c>
       <c r="D171" s="22" t="inlineStr">
         <is>
           <t>2029/06/30</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9006,7 +9006,82 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="15.75" customHeight="1" s="18"/>
+    <row r="183" ht="15.75" customHeight="1" s="18">
+      <c r="A183" s="23" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="23" t="inlineStr">
+        <is>
+          <t>子どもがいない2時間が勝負。カーテン洗濯もリビングの床拭きも、10時前に終わりました</t>
+        </is>
+      </c>
+      <c r="C183" s="23" t="n"/>
+      <c r="D183" s="22" t="inlineStr">
+        <is>
+          <t>2029/09/22</t>
+        </is>
+      </c>
+      <c r="E183" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F183" s="23" t="inlineStr">
+        <is>
+          <t>10月から始めた小掃除、2回目です🧹
+今日やったのはこの3つ。
+・カーテンの洗濯
+・リビングの床拭き
+・長女と次男の棚の整理
+8時15分に始めて、10時前に終わりました。
+【いちばん大事なのは時間帯】
+子どもたちがサッカー練習でいなかったこと。
+練習は8時から10時半まで。
+つまりその時間、家に子どもがいません。
+正直に言うと——
+リビングを広々使って集中して掃除するには
+子どもがいないほうがいいです😅
+いるとどうなるか。
+・床を拭いている横で何かを広げ始める
+・片付けた棚からまた何かを出す
+・「おなかすいた」が入る
+悪気はありません。でも進みません。
+本当は一緒にやったほうが教育になります。
+そちらは冬休みにまとめてやってもらう予定。
+今日は親が集中して終わらせる日と割り切りました。
+【今日の午前中】
+7:20 長男をサッカーの試合で学校へ送る
+その後 洗濯物を干す
+その後 長女と次男をサッカーへ送る
+8:15 ようやく掃除スタート
+午前中フル稼働です💦
+【我が家の土曜の朝サイクル】
+6:00 朝食
+6:30 洗濯
+7:00までに ご飯の片付け・掃除機・
+　　　　　　風呂掃除・トイレ掃除・ゴミ集め
+これを夫婦で協力して終わらせます。
+7時の時点で家が片付いていると
+1日がまったく違います✨
+ちなみに救急箱の整理は
+今日できませんでした。明日に回します。
+1か所ずつ区切っていてよかった。
+全部やろうとしていたら
+終わらなくて落ち込むところでした。
+できなかったら明日。それで済みます。
+【今日の気づき】
+掃除の時間は「作る」より「見つける」。
+・子どもが習い事に行っている時間
+・全員が出払っている時間
+・朝、まだ誰も起きていない時間
+その時間に、1か所だけ。
+これなら続きます。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#大掃除 #小掃除 #片付け #家事 #暮らしの工夫 #3人育児 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="184" ht="15.75" customHeight="1" s="18"/>
     <row r="185" ht="15.75" customHeight="1" s="18"/>
     <row r="186" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -9034,6 +9034,18 @@
 ・リビングの床拭き
 ・長女と次男の棚の整理
 8時15分に始めて、10時前に終わりました。
+【カーテンは洗ったらそのまま吊るす】
+我が家は洗ったらカーテンレールに戻して
+そのまま干します。網戸にしておけば乾きます。
+干す場所を探さなくていいし
+物干しが占領されることもない。
+取り込んで付け直す手間もなし。
+そして、これがいちばん好きなところ。
+風に揺られて、いい香りがふわっと香る🌿
+窓を開けて網戸越しに風が入ってくると
+洗いたてのカーテンが揺れて
+部屋全体がいい匂いになります。
+掃除をしていて、ごほうびのような時間です。
 【いちばん大事なのは時間帯】
 子どもたちがサッカー練習でいなかったこと。
 練習は8時から10時半まで。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9094,7 +9094,87 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="15.75" customHeight="1" s="18"/>
+    <row r="184" ht="15.75" customHeight="1" s="18">
+      <c r="A184" s="23" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="23" t="inlineStr">
+        <is>
+          <t>救急箱と薬箱を整理したら、使わない薬だらけでした。訪問看護師が残したもの・捨てたもの</t>
+        </is>
+      </c>
+      <c r="C184" s="23" t="n"/>
+      <c r="D184" s="22" t="inlineStr">
+        <is>
+          <t>2029/09/29</t>
+        </is>
+      </c>
+      <c r="E184" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F184" s="23" t="inlineStr">
+        <is>
+          <t>小掃除3回目は救急箱と薬箱💊
+棚とチェストを整理したら
+こんなものが出てきました。
+・塩分チャージのタブレット
+　→謎に開封袋が3つ、さらに新品が1つ
+・冷えピタ2箱
+・首にかける小型送風機2つ
+・ハンディファン3つ
+・ホッカイロ多数
+…なぜ😇
+誰も買いすぎているつもりはないのに
+こうなりますよね。
+【まず季節で分けました】
+・夏に使うもの
+・冬に使うもの
+それぞれカゴに入れて棚へ。
+これだけですっきり。
+次に買う前に「夏のカゴ」を見ればいいので
+ハンディファンが4つになることもありません。
+【薬箱：捨てたもの】
+・期限切れの市販薬
+・以前もらった処方薬のうち使わないもの
+期限切れは迷わず処分でいいと思います。
+いざというとき「まだ使えるっけ」と
+考える時間がもったいないので。
+【残した処方薬は3つだけ】
+解熱鎮痛剤・吐き気止め・めまいの薬
+ただし大事なことなので書いておきます。
+処方薬は、そのときの症状と
+その人の体の状態に合わせて出されたもの。
+あとから自己判断で使うことは
+基本的に勧められません。
+迷ったら、かかりつけの医療機関や薬局へ。
+薬局は飲み合わせや期限の相談にも乗ってくれます。
+【救急箱に残したのは7つ】
+湿布／熱さまシート／包帯類／ガーゼ／
+キズパワーパッド／テープ／防水フィルム材
+薬箱と救急箱を分けておくと
+「飲むもの」と「貼る・巻くもの」で
+探す場所が決まります。
+慌てているときほど、これが効きます。
+【置き方】
+使用頻度の高いもの → 取り出しやすい右側
+高くないもの → 左側
+意識しないと、だいたい「入った順」になります。
+ものが減ったので
+何がどこにあるかが分かりやすくなりました✨
+作業時間は1時間かかりませんでした。
+ちなみにここまでの小掃除は
+・和室：1時間半
+・カーテン洗濯・床拭き・棚：1時間45分
+・救急箱・薬箱・チェスト：1時間弱
+どれも午前中で終わる量です。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#大掃除 #小掃除 #救急箱 #片付け #暮らしの工夫 #訪問看護師 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="185" ht="15.75" customHeight="1" s="18"/>
     <row r="186" ht="15.75" customHeight="1" s="18"/>
     <row r="187" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8756,6 +8756,12 @@
 と思っていたけれど違いました。
 見える形になっているほうが
 学年に関係なく動きやすい。
+ちなみにこのリスト
+棚の前とランドセル置き場の2か所に貼っています。
+リストは見る場所になければ意味がありません。
+朝の支度をする場所と
+ランドセルを取りに行く場所。
+どちらにもあれば、見に行かなくて済みます。
 先生にお伝えしたら
 「視覚からのアプローチのほうが
 効果があるかもしれませんね」と共有できました。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -9163,6 +9163,14 @@
 「飲むもの」と「貼る・巻くもの」で
 探す場所が決まります。
 慌てているときほど、これが効きます。
+救急セットは扉の中に入れています。
+理由は埃が入らないようにするため。
+ガーゼや包帯、テープのように
+肌に触れるものは出しっぱなしにしたくない。
+中はカゴで仕切ってあるので
+扉を開ければすぐ取り出せます。
+埃は防ぎたいけれど
+取り出しに手間はかけたくない。その両立です。
 【置き方】
 使用頻度の高いもの → 取り出しやすい右側
 高くないもの → 左側

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -9087,6 +9087,23 @@
 全部やろうとしていたら
 終わらなくて落ち込むところでした。
 できなかったら明日。それで済みます。
+【場所によって「いつやるか」も決める】
+食器戸棚や食品ストックの棚は
+ゴミの日の前日にやると決めています。
+ここは捨てるものがいちばん多く出る場所。
+期限切れの食品、欠けた食器、使わない容器。
+収集日の前日に片付ければ
+ゴミ袋を家に置いておく時間が最短で済みます🗑
+【帰宅後でもできます】
+ここまで「午前中に」と書いてきましたが
+朝しかできないわけではありません。
+セクションで区切ってあるので
+1か所なら帰宅後でもやれてしまいます。
+1〜2時間かかる場所もあれば
+15分で終わる場所もあります。
+全部を一度にやろうとしないから
+空いた時間に差し込める。
+これがこの進め方のいちばんの利点かもしれません。
 【今日の気づき】
 掃除の時間は「作る」より「見つける」。
 ・子どもが習い事に行っている時間

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8903,6 +8903,19 @@
 特に②と③は切実。
 年末に片付け始めても
 粗大ゴミの回収日が間に合わないんです。
+【12月にはほぼ終わっています】
+10月から少しずつ進めておくと
+12月にはほぼ終わっています。
+年末にやるのは
+最後に水場を中心に整えるくらい。
+それで年を越せます。
+これがいちばんの理由かもしれません。
+年末は買い出しや料理で忙しい。
+正直、それ以外の仕事はしたくないんです😅
+年末にまとめてやろうとすると
+いちばん忙しい時期に
+いちばん重い仕事が乗ってきます。
+だから先に済ませておく。
 【我が家のやり方】
 一度に全部はやりません。
 セクションに分けて1か所ずつ。

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8880,7 +8880,11 @@
           <t>大掃除ではなく「小掃除」。朝7時から1時間半で和室が終わったら、1日が驚くほど充実しました</t>
         </is>
       </c>
-      <c r="C181" s="23" t="n"/>
+      <c r="C181" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/12T08:55:05+09:00</t>
+        </is>
+      </c>
       <c r="D181" s="22" t="inlineStr">
         <is>
           <t>2029/09/08</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9223,7 +9223,86 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="15.75" customHeight="1" s="18"/>
+    <row r="185" ht="15.75" customHeight="1" s="18">
+      <c r="A185" s="23" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="23" t="inlineStr">
+        <is>
+          <t>「紙を見てよー」の一言で済むようになりました。朝のやることリストを貼ってからの経過報告</t>
+        </is>
+      </c>
+      <c r="C185" s="23" t="n"/>
+      <c r="D185" s="22" t="inlineStr">
+        <is>
+          <t>2029/10/06</t>
+        </is>
+      </c>
+      <c r="E185" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F185" s="23" t="inlineStr">
+        <is>
+          <t>朝のやることリストを貼ってからの経過報告📋
+我が家では朝のやることリストを紙に書いて
+棚の前とランドセル置き場の2か所に
+貼っています。
+・はみがき
+・ピアノ
+・ボールタッチ
+・朝ごはん、ふとんのかたづけ
+・学校に行く準備
+【次男(小1)】
+もうすでに頭に入っているようで
+一つ一つこなせています✨
+貼ったときは「読めるかな」と思っていましたが
+繰り返すうちに順番ごと覚えてしまったようです。
+【長男(小6)】
+まだ声かけが必要な内容もあります。
+でも歯磨きは言われなくてもできつつあります。
+全部ではないけれど1つずつ減っているのは確か。
+【そして、いちばん楽になったのは…】
+私でした😂
+貼る前は一つ一つ指摘していました。
+「歯磨きした？」「ふとん片付けた？」
+「準備できてる？」
+朝のあいだ中、言い続けている感じ。
+それが今は——
+「紙を見てよー」
+この一言で済みます。
+言う側も疲れるんですよね。
+言うたびに反応を見て、動かなければまた言って。
+朝のいちばん忙しい時間にそれを繰り返す。
+本当にストレスが減りました。
+リストは子どものために作ったつもりでしたが
+いちばん助かったのは私だったかもしれません。
+【ちなみに】
+長男は5:30に起きて
+すぐ携帯ゲームかYouTubeを始めます。
+これは完全に習慣化😇
+誰も何も言っていないのに毎朝きっちり続く。
+楽しいこと、面白いことは
+何も言わなくても続くんだなとしみじみ…
+でも伝えたいのは「やめなさい」ではなく
+「やることを早く終わらせたほうが
+自由時間が増えるよ」という合理性のほう。
+言われてやるのではなく
+そのほうが得だからやる。
+そこまで行けば声かけはいらなくなります。
+まだまだ道のりは長いですが
+見守りつつ、できていることを
+フィードバックしていきたいです。
+「今日は歯磨き、言われる前にやってたね」
+そういう一言を忘れずに。
+伴走していきます😊
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#3人育児 #小学生ママ #やることリスト #見える化 #朝の支度 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="186" ht="15.75" customHeight="1" s="18"/>
     <row r="187" ht="15.75" customHeight="1" s="18"/>
     <row r="188" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8682,7 +8682,11 @@
           <t>保護者面談を3人分。事前に質問メモを作っていったら、短い時間でも聞きたいことが聞けました</t>
         </is>
       </c>
-      <c r="C179" s="23" t="n"/>
+      <c r="C179" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/14T09:06:17+09:00</t>
+        </is>
+      </c>
       <c r="D179" s="22" t="inlineStr">
         <is>
           <t>2029/08/25</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9307,7 +9307,91 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="15.75" customHeight="1" s="18"/>
+    <row r="186" ht="15.75" customHeight="1" s="18">
+      <c r="A186" s="23" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="23" t="inlineStr">
+        <is>
+          <t>ふるさと納税の確定申告をスマホでやろうとして進めなかった原因は、既定ブラウザがChromeだったことでした</t>
+        </is>
+      </c>
+      <c r="C186" s="23" t="n"/>
+      <c r="D186" s="22" t="inlineStr">
+        <is>
+          <t>2029/10/13</t>
+        </is>
+      </c>
+      <c r="E186" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F186" s="23" t="inlineStr">
+        <is>
+          <t>ふるさと納税の確定申告をスマホでやろうとして
+延々と進めなかった話です📱
+原因はまさかのブラウザ設定でした。
+【きっかけ】
+昨年のふるさと納税で
+ワンストップ特例の申請を1つ出し忘れ。
+1つでも出し忘れると確定申告が必要になります。
+【e-Taxは思いのほか楽でした】
+いちばん驚いたのが
+源泉徴収票は写真を撮るとデータを
+取り込んでくれること📷
+数字を1つずつ入力するものだと思っていたので
+拍子抜けしました。
+ただし注意点。
+忘れた1件だけでなく
+その年のふるさと納税は全部入力が必要です。
+（確定申告をするとワンストップ特例が無効になるため）
+とはいえ、寄付金受領証明書を見ながら
+書いてあるとおりに入力するだけです。
+【ところが進めない】
+携帯からの入力がずっとうまくいかない。
+何度やっても先に進めない。
+エラーの原因がまったく想像できませんでした。
+【原因】
+最初に開くサイトが
+Chromeで開かれる設定になっていたこと。
+そのせいでSafariに移動できず止まっていました。
+設定を変えただけでさくさく進みました✨
+国税庁の推奨環境は
+・iPhone → Safari
+・Android → Chrome
+自分で設定した覚えもないんです。
+画面には「ブラウザが原因です」とは
+書いてくれません。
+知らずに苦労している人がいたら
+教えてあげたいと思って書きました。
+【医療費控除と比べてみました】
+医療費控除は(医療費−10万円)×税率が目安。
+領収書を集めて集計して入力して…
+かなりの手間で還付は数千円ということも。
+ふるさと納税は2万円の寄付なら
+18,000円ぶん税金が軽くなります。
+入力は証明書を見ながら写すだけ。
+手間あたりの効果がまるで違います。
+【ただし「18,000円が現金で戻る」ではありません】
+・所得税分 → 確定申告後に現金で還付
+・住民税の基本分 → 翌年度の住民税が安くなる
+・住民税の特例分 → 翌年度の住民税が安くなる
+口座に振り込まれるのは所得税分だけ。
+残りは翌年6月以降の住民税が減る形です。
+「思ったより入金が少ない」と感じるのは
+たぶんこれが理由。
+損ではなく受け取り方が違うだけです。
+※金額は目安です。所得や家族構成で変わります。
+※上限を超えると自己負担が2,000円では
+　済まないので、寄付前にシミュレーションを。
+未申告なら、申告したほうがいいです😊
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#ふるさと納税 #確定申告 #eTax #お金の管理 #節税 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="187" ht="15.75" customHeight="1" s="18"/>
     <row r="188" ht="15.75" customHeight="1" s="18"/>
     <row r="189" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9392,7 +9392,107 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="15.75" customHeight="1" s="18"/>
+    <row r="187" ht="15.75" customHeight="1" s="18">
+      <c r="A187" s="23" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="23" t="inlineStr">
+        <is>
+          <t>「じゃあ、もう一回頑張ってみる？」に大きく首を振る次男。計算カード1分29秒に悔し泣きした夜</t>
+        </is>
+      </c>
+      <c r="C187" s="23" t="n"/>
+      <c r="D187" s="22" t="inlineStr">
+        <is>
+          <t>2029/10/20</t>
+        </is>
+      </c>
+      <c r="E187" s="23" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F187" s="23" t="inlineStr">
+        <is>
+          <t>サッカーから帰ってぐったりの次男。
+寝る時間の夜8時から宿題と向き合った夜の話です😢
+昨日はサッカーの練習日。
+でも宿題が終わっていませんでした。
+「帰ってきたらやろうね」と約束して送り出し
+帰宅後はお風呂、夕飯で気づけば夜8時。
+小1の次男は8時に寝る時間です。
+本来ならもう布団の中。
+それでも本人は「やる」と言って
+最後の力を振り絞って机に向かいました。
+【最後に残っていたのは計算カード】
+次男は1分以内を目指しています。
+結果は1分29秒。
+本人としては不甲斐ない結果でした。
+【でもこの日は違いました】
+普段の次男は
+ちらっと答えを見ながらやっています。
+でもこの日は答えを見ずに
+自分の頭の中で計算していました。
+横で見ていて分かりました。
+考えている時間がいつもと違うんです。
+つまり——
+いつもより遅いのは
+いつもより真剣にやった証拠でした。
+でも本人はそう受け取りません。
+【床に突っ伏して、静かに泣いていました】
+時折、床を叩いて。
+わんわんではなく、声を出さずに。
+次男は気持ちを言葉にするのが得意ではありません。
+聞いても理由は出てきません。
+なので、こちらから言葉にしてみました。
+「タイムが遅かったから、悔しかった？」
+うんと頷いて、そこから大泣き。
+当たっていたようです。
+抱きしめて、見ていたことを伝えました。
+・今日はカンニングしなかったね
+・自分の頭で全部考えてたね
+・疲れてたのに宿題やったね
+【そして聞いてみました】
+「じゃあ、もう一回頑張ってみる？」
+大きく首を振って、拒否😂
+……ですよね。
+次男の課題は
+「最後まで粘り強くやり抜く力が足りない」こと。
+想定内です。
+でもあわよくば頑張ってくれるかなぁという
+期待もちょっとだけありました。
+見られませんでした😇
+【それでも意思は尊重しました】
+もう夜8時過ぎ、疲れ切っていて
+すでに泣くほど力を出し切っている。
+ここでもう一回やらせても
+たぶんタイムは落ちて、もっと嫌になるだけ。
+悔しさは本人のものです。
+【戦っていた相手は計算カードだけじゃない】
+・サッカー2時間ぶんの疲労感
+・本来なら寝ている夜8時という時間
+・答えを見たくなる気持ち
+疲れている日ほど近道を使いたくなるはず。
+それなのにその日に限って正面からやった。
+あの状態で最後までやりきったこと自体が
+立派でした✨
+【悔し泣きは、少し前までなかったものです】
+少し前まではタイムが遅くても
+「ふーん」で終わっていました。
+悔しいと思うには目標がいります。
+「1分以内」という自分の目標があって
+はじめて1分29秒が悔しくなる。
+床を叩いて泣けるくらい
+本気になれるものができた。
+それは前に進んでいるということだと思います。
+明日は頑張れると信じて
+今日もまた計算カードを出します😊
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#小1 #3人育児 #子どもの成長 #計算カード #宿題 #悔し涙 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="188" ht="15.75" customHeight="1" s="18"/>
     <row r="189" ht="15.75" customHeight="1" s="18"/>
     <row r="190" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -1628,14 +1628,10 @@
           <t>2026/03/15</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>2026/10/24</t>
-        </is>
-      </c>
+      <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -1669,14 +1665,10 @@
           <t>2026/03/16</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>2026/10/31</t>
-        </is>
-      </c>
+      <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -1710,14 +1702,10 @@
           <t>2026/03/19</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>2026/11/07</t>
-        </is>
-      </c>
+      <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -1751,14 +1739,10 @@
           <t>2026/06/04</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>2026/11/14</t>
-        </is>
-      </c>
+      <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -1792,14 +1776,10 @@
           <t>2026/03/23</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
+      <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -1833,14 +1813,10 @@
           <t>2026/03/24</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>2026/11/28</t>
-        </is>
-      </c>
+      <c r="D34" s="6" t="n"/>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -1874,14 +1850,10 @@
           <t>2026/03/25</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>2026/12/05</t>
-        </is>
-      </c>
+      <c r="D35" s="6" t="n"/>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -1917,7 +1889,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>2026/12/12</t>
+          <t>2026/10/24</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1957,14 +1929,10 @@
           <t>2026/04/03</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>2026/12/19</t>
-        </is>
-      </c>
+      <c r="D37" s="6" t="n"/>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -1998,14 +1966,10 @@
           <t>2026/04/04</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>2026/12/26</t>
-        </is>
-      </c>
+      <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -2039,14 +2003,10 @@
           <t>2026/04/07</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>2027/01/02</t>
-        </is>
-      </c>
+      <c r="D39" s="6" t="n"/>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -2080,14 +2040,10 @@
           <t>2026/04/12</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>2027/01/09</t>
-        </is>
-      </c>
+      <c r="D40" s="6" t="n"/>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -2121,14 +2077,10 @@
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>2027/01/16</t>
-        </is>
-      </c>
+      <c r="D41" s="6" t="n"/>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -2164,7 +2116,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>2027/01/23</t>
+          <t>2026/10/27</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2203,14 +2155,10 @@
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
+      <c r="D43" s="6" t="n"/>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -2245,14 +2193,10 @@
           <t>2026/05/21</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/06</t>
-        </is>
-      </c>
+      <c r="D44" s="9" t="n"/>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -2284,7 +2228,7 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>2027/02/13</t>
+          <t>2026/10/29</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -2321,14 +2265,10 @@
           <t>2026/04/25</t>
         </is>
       </c>
-      <c r="D46" s="0" t="inlineStr">
-        <is>
-          <t>2027/02/20</t>
-        </is>
-      </c>
+      <c r="D46" s="0" t="n"/>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
@@ -2360,14 +2300,10 @@
           <t>2026/04/26</t>
         </is>
       </c>
-      <c r="D47" s="0" t="inlineStr">
-        <is>
-          <t>2027/02/27</t>
-        </is>
-      </c>
+      <c r="D47" s="0" t="n"/>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F47" s="19" t="inlineStr">
@@ -2399,14 +2335,10 @@
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="D48" s="0" t="inlineStr">
-        <is>
-          <t>2027/03/06</t>
-        </is>
-      </c>
+      <c r="D48" s="0" t="n"/>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
@@ -2438,14 +2370,10 @@
           <t>2026/07/02</t>
         </is>
       </c>
-      <c r="D49" s="0" t="inlineStr">
-        <is>
-          <t>2027/03/13</t>
-        </is>
-      </c>
+      <c r="D49" s="0" t="n"/>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F49" s="19" t="inlineStr">
@@ -2477,14 +2405,10 @@
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="D50" s="0" t="inlineStr">
-        <is>
-          <t>2027/03/20</t>
-        </is>
-      </c>
+      <c r="D50" s="0" t="n"/>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F50" s="20" t="inlineStr">
@@ -2516,14 +2440,10 @@
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="D51" s="0" t="inlineStr">
-        <is>
-          <t>2027/03/27</t>
-        </is>
-      </c>
+      <c r="D51" s="0" t="n"/>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F51" s="19" t="inlineStr">
@@ -2555,14 +2475,10 @@
           <t>2026/05/09</t>
         </is>
       </c>
-      <c r="D52" s="0" t="inlineStr">
-        <is>
-          <t>2027/04/03</t>
-        </is>
-      </c>
+      <c r="D52" s="0" t="n"/>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F52" s="20" t="inlineStr">
@@ -2596,7 +2512,7 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>2027/04/10</t>
+          <t>2026/10/31</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2633,14 +2549,10 @@
           <t>2026/07/09</t>
         </is>
       </c>
-      <c r="D54" s="0" t="inlineStr">
-        <is>
-          <t>2027/04/17</t>
-        </is>
-      </c>
+      <c r="D54" s="0" t="n"/>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F54" s="20" t="inlineStr">
@@ -2672,14 +2584,10 @@
           <t>2026/05/12</t>
         </is>
       </c>
-      <c r="D55" s="0" t="inlineStr">
-        <is>
-          <t>2027/04/24</t>
-        </is>
-      </c>
+      <c r="D55" s="0" t="n"/>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F55" s="19" t="inlineStr">
@@ -2711,14 +2619,10 @@
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="D56" s="0" t="inlineStr">
-        <is>
-          <t>2027/05/01</t>
-        </is>
-      </c>
+      <c r="D56" s="0" t="n"/>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F56" s="20" t="inlineStr">
@@ -2750,14 +2654,10 @@
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="D57" s="0" t="inlineStr">
-        <is>
-          <t>2027/05/08</t>
-        </is>
-      </c>
+      <c r="D57" s="0" t="n"/>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F57" s="19" t="inlineStr">
@@ -2789,14 +2689,10 @@
           <t>2026/07/23</t>
         </is>
       </c>
-      <c r="D58" s="0" t="inlineStr">
-        <is>
-          <t>2027/05/15</t>
-        </is>
-      </c>
+      <c r="D58" s="0" t="n"/>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F58" s="20" t="inlineStr">
@@ -2828,14 +2724,10 @@
           <t>2026/07/16</t>
         </is>
       </c>
-      <c r="D59" s="0" t="inlineStr">
-        <is>
-          <t>2027/05/22</t>
-        </is>
-      </c>
+      <c r="D59" s="0" t="n"/>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F59" s="19" t="inlineStr">
@@ -2867,14 +2759,10 @@
           <t>2026/07/20</t>
         </is>
       </c>
-      <c r="D60" s="0" t="inlineStr">
-        <is>
-          <t>2027/05/29</t>
-        </is>
-      </c>
+      <c r="D60" s="0" t="n"/>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F60" s="20" t="inlineStr">
@@ -2947,7 +2835,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>2027/06/05</t>
+          <t>2026/11/03</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
@@ -2984,14 +2872,10 @@
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="D63" s="0" t="inlineStr">
-        <is>
-          <t>2027/06/12</t>
-        </is>
-      </c>
+      <c r="D63" s="0" t="n"/>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F63" s="19" t="inlineStr">
@@ -3023,14 +2907,10 @@
           <t>2026/08/03</t>
         </is>
       </c>
-      <c r="D64" s="0" t="inlineStr">
-        <is>
-          <t>2027/06/19</t>
-        </is>
-      </c>
+      <c r="D64" s="0" t="n"/>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
@@ -3062,14 +2942,10 @@
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="D65" s="0" t="inlineStr">
-        <is>
-          <t>2027/06/26</t>
-        </is>
-      </c>
+      <c r="D65" s="0" t="n"/>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F65" s="19" t="inlineStr">
@@ -3101,14 +2977,10 @@
           <t>2026/06/01</t>
         </is>
       </c>
-      <c r="D66" s="0" t="inlineStr">
-        <is>
-          <t>2027/07/03</t>
-        </is>
-      </c>
+      <c r="D66" s="0" t="n"/>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
@@ -3140,14 +3012,10 @@
           <t>2026/08/06</t>
         </is>
       </c>
-      <c r="D67" s="0" t="inlineStr">
-        <is>
-          <t>2027/07/10</t>
-        </is>
-      </c>
+      <c r="D67" s="0" t="n"/>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F67" s="19" t="inlineStr">
@@ -3179,14 +3047,10 @@
           <t>2026/09/30T09:07:03+09:00</t>
         </is>
       </c>
-      <c r="D68" s="0" t="inlineStr">
-        <is>
-          <t>2027/07/17</t>
-        </is>
-      </c>
+      <c r="D68" s="0" t="n"/>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
@@ -3218,14 +3082,10 @@
           <t>2026/10/05T09:07:36+09:00</t>
         </is>
       </c>
-      <c r="D69" s="0" t="inlineStr">
-        <is>
-          <t>2027/07/24</t>
-        </is>
-      </c>
+      <c r="D69" s="0" t="n"/>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F69" s="19" t="inlineStr">
@@ -3257,14 +3117,10 @@
           <t>2026/10/07T09:05:13+09:00</t>
         </is>
       </c>
-      <c r="D70" s="0" t="inlineStr">
-        <is>
-          <t>2027/07/31</t>
-        </is>
-      </c>
+      <c r="D70" s="0" t="n"/>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
@@ -3335,14 +3191,10 @@
           <t>2026/06/04</t>
         </is>
       </c>
-      <c r="D72" s="0" t="inlineStr">
-        <is>
-          <t>2027/08/07</t>
-        </is>
-      </c>
+      <c r="D72" s="0" t="n"/>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
@@ -3374,14 +3226,10 @@
           <t>2026/06/04</t>
         </is>
       </c>
-      <c r="D73" s="0" t="inlineStr">
-        <is>
-          <t>2027/08/14</t>
-        </is>
-      </c>
+      <c r="D73" s="0" t="n"/>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F73" s="19" t="inlineStr">
@@ -3413,14 +3261,10 @@
           <t>2026/06/05</t>
         </is>
       </c>
-      <c r="D74" s="0" t="inlineStr">
-        <is>
-          <t>2027/08/21</t>
-        </is>
-      </c>
+      <c r="D74" s="0" t="n"/>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
@@ -3454,7 +3298,7 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>2027/08/28</t>
+          <t>2026/11/05</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3491,14 +3335,10 @@
           <t>2026/06/07</t>
         </is>
       </c>
-      <c r="D76" s="0" t="inlineStr">
-        <is>
-          <t>2027/09/04</t>
-        </is>
-      </c>
+      <c r="D76" s="0" t="n"/>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
@@ -3530,14 +3370,10 @@
           <t>2026/06/08</t>
         </is>
       </c>
-      <c r="D77" s="0" t="inlineStr">
-        <is>
-          <t>2027/09/11</t>
-        </is>
-      </c>
+      <c r="D77" s="0" t="n"/>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F77" s="19" t="inlineStr">
@@ -3569,14 +3405,10 @@
           <t>2026/06/08</t>
         </is>
       </c>
-      <c r="D78" s="0" t="inlineStr">
-        <is>
-          <t>2027/09/18</t>
-        </is>
-      </c>
+      <c r="D78" s="0" t="n"/>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
@@ -3610,7 +3442,7 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>2027/09/25</t>
+          <t>2026/11/07</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3647,14 +3479,10 @@
           <t>2026/06/08</t>
         </is>
       </c>
-      <c r="D80" s="0" t="inlineStr">
-        <is>
-          <t>2027/10/02</t>
-        </is>
-      </c>
+      <c r="D80" s="0" t="n"/>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -3686,14 +3514,10 @@
           <t>2026/06/11</t>
         </is>
       </c>
-      <c r="D81" s="0" t="inlineStr">
-        <is>
-          <t>2027/10/09</t>
-        </is>
-      </c>
+      <c r="D81" s="0" t="n"/>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F81" s="19" t="inlineStr">
@@ -3725,14 +3549,10 @@
           <t>2026/06/11</t>
         </is>
       </c>
-      <c r="D82" s="0" t="inlineStr">
-        <is>
-          <t>2027/10/16</t>
-        </is>
-      </c>
+      <c r="D82" s="0" t="n"/>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
@@ -3764,14 +3584,10 @@
           <t>2026/06/13</t>
         </is>
       </c>
-      <c r="D83" s="0" t="inlineStr">
-        <is>
-          <t>2027/10/23</t>
-        </is>
-      </c>
+      <c r="D83" s="0" t="n"/>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F83" s="19" t="inlineStr">
@@ -3803,14 +3619,10 @@
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="D84" s="0" t="inlineStr">
-        <is>
-          <t>2027/10/30</t>
-        </is>
-      </c>
+      <c r="D84" s="0" t="n"/>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
@@ -3844,7 +3656,7 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2026/11/10</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -3881,14 +3693,10 @@
           <t>2026/06/16</t>
         </is>
       </c>
-      <c r="D86" s="0" t="inlineStr">
-        <is>
-          <t>2027/11/13</t>
-        </is>
-      </c>
+      <c r="D86" s="0" t="n"/>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
@@ -3920,14 +3728,10 @@
           <t>2026/06/18</t>
         </is>
       </c>
-      <c r="D87" s="0" t="inlineStr">
-        <is>
-          <t>2027/11/20</t>
-        </is>
-      </c>
+      <c r="D87" s="0" t="n"/>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F87" s="19" t="inlineStr">
@@ -3959,14 +3763,10 @@
           <t>2026/06/18</t>
         </is>
       </c>
-      <c r="D88" s="0" t="inlineStr">
-        <is>
-          <t>2027/11/27</t>
-        </is>
-      </c>
+      <c r="D88" s="0" t="n"/>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
@@ -4000,7 +3800,7 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>2027/12/04</t>
+          <t>2026/11/12</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4037,14 +3837,10 @@
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="D90" s="0" t="inlineStr">
-        <is>
-          <t>2027/12/11</t>
-        </is>
-      </c>
+      <c r="D90" s="0" t="n"/>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
@@ -4076,14 +3872,10 @@
           <t>2026/09/21T09:06:28+09:00</t>
         </is>
       </c>
-      <c r="D91" s="0" t="inlineStr">
-        <is>
-          <t>2027/12/18</t>
-        </is>
-      </c>
+      <c r="D91" s="0" t="n"/>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F91" s="19" t="inlineStr">
@@ -4115,14 +3907,10 @@
           <t>2026/06/20</t>
         </is>
       </c>
-      <c r="D92" s="0" t="inlineStr">
-        <is>
-          <t>2027/12/25</t>
-        </is>
-      </c>
+      <c r="D92" s="0" t="n"/>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -4154,14 +3942,10 @@
           <t>2026/06/20</t>
         </is>
       </c>
-      <c r="D93" s="0" t="inlineStr">
-        <is>
-          <t>2028/01/01</t>
-        </is>
-      </c>
+      <c r="D93" s="0" t="n"/>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F93" s="19" t="inlineStr">
@@ -4193,14 +3977,10 @@
           <t>2026/09/23T09:07:32+09:00</t>
         </is>
       </c>
-      <c r="D94" s="0" t="inlineStr">
-        <is>
-          <t>2028/01/08</t>
-        </is>
-      </c>
+      <c r="D94" s="0" t="n"/>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
@@ -4232,14 +4012,10 @@
           <t>2026/06/20</t>
         </is>
       </c>
-      <c r="D95" s="0" t="inlineStr">
-        <is>
-          <t>2028/01/15</t>
-        </is>
-      </c>
+      <c r="D95" s="0" t="n"/>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F95" s="19" t="inlineStr">
@@ -4271,14 +4047,10 @@
           <t>2026/06/20</t>
         </is>
       </c>
-      <c r="D96" s="0" t="inlineStr">
-        <is>
-          <t>2028/01/22</t>
-        </is>
-      </c>
+      <c r="D96" s="0" t="n"/>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
@@ -4310,14 +4082,10 @@
           <t>2026/06/22</t>
         </is>
       </c>
-      <c r="D97" s="0" t="inlineStr">
-        <is>
-          <t>2028/01/29</t>
-        </is>
-      </c>
+      <c r="D97" s="0" t="n"/>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F97" s="19" t="inlineStr">
@@ -4349,14 +4117,10 @@
           <t>2026/06/23</t>
         </is>
       </c>
-      <c r="D98" s="0" t="inlineStr">
-        <is>
-          <t>2028/02/05</t>
-        </is>
-      </c>
+      <c r="D98" s="0" t="n"/>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
@@ -4390,7 +4154,7 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>2028/02/12</t>
+          <t>2026/11/14</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4427,14 +4191,10 @@
           <t>2026/06/23</t>
         </is>
       </c>
-      <c r="D100" s="0" t="inlineStr">
-        <is>
-          <t>2028/02/19</t>
-        </is>
-      </c>
+      <c r="D100" s="0" t="n"/>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -4466,14 +4226,10 @@
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="D101" s="0" t="inlineStr">
-        <is>
-          <t>2028/02/26</t>
-        </is>
-      </c>
+      <c r="D101" s="0" t="n"/>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F101" s="19" t="inlineStr">
@@ -4505,14 +4261,10 @@
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="D102" s="0" t="inlineStr">
-        <is>
-          <t>2028/03/04</t>
-        </is>
-      </c>
+      <c r="D102" s="0" t="n"/>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
@@ -4544,14 +4296,10 @@
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="D103" s="0" t="inlineStr">
-        <is>
-          <t>2028/03/11</t>
-        </is>
-      </c>
+      <c r="D103" s="0" t="n"/>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F103" s="19" t="inlineStr">
@@ -4583,14 +4331,10 @@
           <t>2026/09/28T09:14:30+09:00</t>
         </is>
       </c>
-      <c r="D104" s="0" t="inlineStr">
-        <is>
-          <t>2028/03/18</t>
-        </is>
-      </c>
+      <c r="D104" s="0" t="n"/>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -4624,7 +4368,7 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>2028/03/25</t>
+          <t>2026/11/17</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
@@ -4661,14 +4405,10 @@
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="D106" s="0" t="inlineStr">
-        <is>
-          <t>2028/04/01</t>
-        </is>
-      </c>
+      <c r="D106" s="0" t="n"/>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
@@ -4700,14 +4440,10 @@
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="D107" s="0" t="inlineStr">
-        <is>
-          <t>2028/04/08</t>
-        </is>
-      </c>
+      <c r="D107" s="0" t="n"/>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F107" s="19" t="inlineStr">
@@ -4739,14 +4475,10 @@
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="D108" s="0" t="inlineStr">
-        <is>
-          <t>2028/04/15</t>
-        </is>
-      </c>
+      <c r="D108" s="0" t="n"/>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
@@ -4778,14 +4510,10 @@
           <t>2026/07/15</t>
         </is>
       </c>
-      <c r="D109" s="22" t="inlineStr">
-        <is>
-          <t>2028/04/22</t>
-        </is>
-      </c>
+      <c r="D109" s="22" t="n"/>
       <c r="E109" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F109" s="21" t="inlineStr">
@@ -4820,14 +4548,10 @@
           <t>2026/07/03</t>
         </is>
       </c>
-      <c r="D110" s="22" t="inlineStr">
-        <is>
-          <t>2028/04/29</t>
-        </is>
-      </c>
+      <c r="D110" s="22" t="n"/>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
@@ -4866,14 +4590,10 @@
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="D111" s="22" t="inlineStr">
-        <is>
-          <t>2028/05/06</t>
-        </is>
-      </c>
+      <c r="D111" s="22" t="n"/>
       <c r="E111" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F111" s="21" t="inlineStr">
@@ -4909,14 +4629,10 @@
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="D112" s="22" t="inlineStr">
-        <is>
-          <t>2028/05/13</t>
-        </is>
-      </c>
+      <c r="D112" s="22" t="n"/>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
@@ -4952,14 +4668,10 @@
           <t>2026/07/07</t>
         </is>
       </c>
-      <c r="D113" s="22" t="inlineStr">
-        <is>
-          <t>2028/05/20</t>
-        </is>
-      </c>
+      <c r="D113" s="22" t="n"/>
       <c r="E113" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F113" s="21" t="inlineStr">
@@ -4996,14 +4708,10 @@
           <t>2026/07/18</t>
         </is>
       </c>
-      <c r="D114" s="22" t="inlineStr">
-        <is>
-          <t>2028/05/27</t>
-        </is>
-      </c>
+      <c r="D114" s="22" t="n"/>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
@@ -5042,7 +4750,7 @@
       </c>
       <c r="D115" s="22" t="inlineStr">
         <is>
-          <t>2028/06/03</t>
+          <t>2026/11/19</t>
         </is>
       </c>
       <c r="E115" s="21" t="inlineStr">
@@ -5085,7 +4793,7 @@
       </c>
       <c r="D116" s="22" t="inlineStr">
         <is>
-          <t>2028/06/10</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
@@ -5128,14 +4836,10 @@
           <t>2026/07/10</t>
         </is>
       </c>
-      <c r="D117" s="22" t="inlineStr">
-        <is>
-          <t>2028/06/17</t>
-        </is>
-      </c>
+      <c r="D117" s="22" t="n"/>
       <c r="E117" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F117" s="21" t="inlineStr">
@@ -5174,7 +4878,7 @@
       </c>
       <c r="D118" s="22" t="inlineStr">
         <is>
-          <t>2028/06/24</t>
+          <t>2026/11/24</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
@@ -5217,14 +4921,10 @@
           <t>2026/07/17</t>
         </is>
       </c>
-      <c r="D119" s="22" t="inlineStr">
-        <is>
-          <t>2028/07/01</t>
-        </is>
-      </c>
+      <c r="D119" s="22" t="n"/>
       <c r="E119" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F119" s="21" t="inlineStr">
@@ -5264,7 +4964,7 @@
       </c>
       <c r="D120" s="22" t="inlineStr">
         <is>
-          <t>2028/07/08</t>
+          <t>2026/11/26</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
@@ -5306,14 +5006,10 @@
           <t>2026/07/12</t>
         </is>
       </c>
-      <c r="D121" s="22" t="inlineStr">
-        <is>
-          <t>2028/07/15</t>
-        </is>
-      </c>
+      <c r="D121" s="22" t="n"/>
       <c r="E121" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F121" s="21" t="inlineStr">
@@ -5353,7 +5049,7 @@
       </c>
       <c r="D122" s="22" t="inlineStr">
         <is>
-          <t>2028/07/22</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
@@ -5398,7 +5094,7 @@
       </c>
       <c r="D123" s="22" t="inlineStr">
         <is>
-          <t>2028/07/29</t>
+          <t>2026/12/01</t>
         </is>
       </c>
       <c r="E123" s="21" t="inlineStr">
@@ -5441,14 +5137,10 @@
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="D124" s="22" t="inlineStr">
-        <is>
-          <t>2028/08/05</t>
-        </is>
-      </c>
+      <c r="D124" s="22" t="n"/>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
@@ -5485,14 +5177,10 @@
           <t>2026/07/17</t>
         </is>
       </c>
-      <c r="D125" s="22" t="inlineStr">
-        <is>
-          <t>2028/08/12</t>
-        </is>
-      </c>
+      <c r="D125" s="22" t="n"/>
       <c r="E125" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F125" s="21" t="inlineStr">
@@ -5532,7 +5220,7 @@
       </c>
       <c r="D126" s="22" t="inlineStr">
         <is>
-          <t>2028/08/19</t>
+          <t>2026/12/03</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
@@ -5578,7 +5266,7 @@
       </c>
       <c r="D127" s="22" t="inlineStr">
         <is>
-          <t>2028/08/26</t>
+          <t>2026/12/05</t>
         </is>
       </c>
       <c r="E127" s="21" t="inlineStr">
@@ -5623,7 +5311,7 @@
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>2028/09/02</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
@@ -5668,7 +5356,7 @@
       </c>
       <c r="D129" s="22" t="inlineStr">
         <is>
-          <t>2028/09/09</t>
+          <t>2026/12/10</t>
         </is>
       </c>
       <c r="E129" s="21" t="inlineStr">
@@ -5711,14 +5399,10 @@
           <t>2026/07/21</t>
         </is>
       </c>
-      <c r="D130" s="22" t="inlineStr">
-        <is>
-          <t>2028/09/16</t>
-        </is>
-      </c>
+      <c r="D130" s="22" t="n"/>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
@@ -5757,14 +5441,10 @@
           <t>2026/07/23</t>
         </is>
       </c>
-      <c r="D131" s="22" t="inlineStr">
-        <is>
-          <t>2028/09/23</t>
-        </is>
-      </c>
+      <c r="D131" s="22" t="n"/>
       <c r="E131" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F131" s="21" t="inlineStr">
@@ -5806,7 +5486,7 @@
       </c>
       <c r="D132" s="22" t="inlineStr">
         <is>
-          <t>2028/09/30</t>
+          <t>2026/12/12</t>
         </is>
       </c>
       <c r="E132" s="21" t="inlineStr">
@@ -5849,14 +5529,10 @@
           <t>2026/07/29</t>
         </is>
       </c>
-      <c r="D133" s="22" t="inlineStr">
-        <is>
-          <t>2028/10/07</t>
-        </is>
-      </c>
+      <c r="D133" s="22" t="n"/>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
@@ -5897,7 +5573,7 @@
       </c>
       <c r="D134" s="22" t="inlineStr">
         <is>
-          <t>2028/10/14</t>
+          <t>2026/12/15</t>
         </is>
       </c>
       <c r="E134" s="21" t="inlineStr">
@@ -5939,14 +5615,10 @@
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="D135" s="22" t="inlineStr">
-        <is>
-          <t>2028/10/21</t>
-        </is>
-      </c>
+      <c r="D135" s="22" t="n"/>
       <c r="E135" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F135" s="21" t="inlineStr">
@@ -5985,14 +5657,10 @@
           <t>2026/08/01</t>
         </is>
       </c>
-      <c r="D136" s="22" t="inlineStr">
-        <is>
-          <t>2028/10/28</t>
-        </is>
-      </c>
+      <c r="D136" s="22" t="n"/>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
@@ -6032,7 +5700,7 @@
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>2028/11/04</t>
+          <t>2026/12/17</t>
         </is>
       </c>
       <c r="E137" s="21" t="inlineStr">
@@ -6075,14 +5743,10 @@
           <t>2026/08/02</t>
         </is>
       </c>
-      <c r="D138" s="22" t="inlineStr">
-        <is>
-          <t>2028/11/11</t>
-        </is>
-      </c>
+      <c r="D138" s="22" t="n"/>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
@@ -6123,7 +5787,7 @@
       </c>
       <c r="D139" s="22" t="inlineStr">
         <is>
-          <t>2028/11/18</t>
+          <t>2026/12/19</t>
         </is>
       </c>
       <c r="E139" s="21" t="inlineStr">
@@ -6168,14 +5832,10 @@
           <t>2026/08/04</t>
         </is>
       </c>
-      <c r="D140" s="22" t="inlineStr">
-        <is>
-          <t>2028/11/25</t>
-        </is>
-      </c>
+      <c r="D140" s="22" t="n"/>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
@@ -6215,7 +5875,7 @@
       </c>
       <c r="D141" s="22" t="inlineStr">
         <is>
-          <t>2028/12/02</t>
+          <t>2026/12/22</t>
         </is>
       </c>
       <c r="E141" s="21" t="inlineStr">
@@ -6259,14 +5919,10 @@
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="D142" s="22" t="inlineStr">
-        <is>
-          <t>2028/12/09</t>
-        </is>
-      </c>
+      <c r="D142" s="22" t="n"/>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
@@ -6308,7 +5964,7 @@
       </c>
       <c r="D143" s="22" t="inlineStr">
         <is>
-          <t>2028/12/16</t>
+          <t>2026/12/24</t>
         </is>
       </c>
       <c r="E143" s="21" t="inlineStr">
@@ -6354,7 +6010,7 @@
       </c>
       <c r="D144" s="22" t="inlineStr">
         <is>
-          <t>2028/12/23</t>
+          <t>2026/12/26</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
@@ -6402,7 +6058,7 @@
       </c>
       <c r="D145" s="22" t="inlineStr">
         <is>
-          <t>2028/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="E145" s="21" t="inlineStr">
@@ -6442,14 +6098,10 @@
         </is>
       </c>
       <c r="C146" s="23" t="n"/>
-      <c r="D146" s="22" t="inlineStr">
-        <is>
-          <t>2029/01/06</t>
-        </is>
-      </c>
+      <c r="D146" s="22" t="n"/>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
@@ -6488,14 +6140,10 @@
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="D147" s="22" t="inlineStr">
-        <is>
-          <t>2029/01/13</t>
-        </is>
-      </c>
+      <c r="D147" s="22" t="n"/>
       <c r="E147" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F147" s="21" t="inlineStr">
@@ -6536,7 +6184,7 @@
       </c>
       <c r="D148" s="22" t="inlineStr">
         <is>
-          <t>2029/01/20</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
@@ -6586,7 +6234,7 @@
       </c>
       <c r="D149" s="22" t="inlineStr">
         <is>
-          <t>2029/01/27</t>
+          <t>2027/01/02</t>
         </is>
       </c>
       <c r="E149" s="21" t="inlineStr">
@@ -6634,7 +6282,7 @@
       </c>
       <c r="D150" s="22" t="inlineStr">
         <is>
-          <t>2029/02/03</t>
+          <t>2027/01/05</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
@@ -6684,14 +6332,10 @@
         </is>
       </c>
       <c r="C151" s="21" t="n"/>
-      <c r="D151" s="22" t="inlineStr">
-        <is>
-          <t>2029/02/10</t>
-        </is>
-      </c>
+      <c r="D151" s="22" t="n"/>
       <c r="E151" s="21" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F151" s="21" t="inlineStr">
@@ -6738,14 +6382,10 @@
           <t>2026/08/23</t>
         </is>
       </c>
-      <c r="D152" s="22" t="inlineStr">
-        <is>
-          <t>2029/02/17</t>
-        </is>
-      </c>
+      <c r="D152" s="22" t="n"/>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
@@ -6797,7 +6437,7 @@
       </c>
       <c r="D153" s="22" t="inlineStr">
         <is>
-          <t>2029/02/24</t>
+          <t>2027/01/07</t>
         </is>
       </c>
       <c r="E153" s="21" t="inlineStr">
@@ -6865,7 +6505,7 @@
       </c>
       <c r="D154" s="22" t="inlineStr">
         <is>
-          <t>2029/03/03</t>
+          <t>2027/01/09</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
@@ -6924,7 +6564,7 @@
       </c>
       <c r="D155" s="22" t="inlineStr">
         <is>
-          <t>2029/03/10</t>
+          <t>2027/01/12</t>
         </is>
       </c>
       <c r="E155" s="21" t="inlineStr">
@@ -6978,7 +6618,7 @@
       </c>
       <c r="D156" s="22" t="inlineStr">
         <is>
-          <t>2029/03/17</t>
+          <t>2027/01/14</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
@@ -7035,7 +6675,7 @@
       </c>
       <c r="D157" s="22" t="inlineStr">
         <is>
-          <t>2029/03/24</t>
+          <t>2027/01/16</t>
         </is>
       </c>
       <c r="E157" s="21" t="inlineStr">
@@ -7091,7 +6731,7 @@
       </c>
       <c r="D158" s="22" t="inlineStr">
         <is>
-          <t>2029/03/31</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
@@ -7154,7 +6794,7 @@
       </c>
       <c r="D159" s="22" t="inlineStr">
         <is>
-          <t>2029/04/07</t>
+          <t>2027/01/21</t>
         </is>
       </c>
       <c r="E159" s="21" t="inlineStr">
@@ -7234,14 +6874,10 @@
           <t>2026/09/06T08:00:00+09:00</t>
         </is>
       </c>
-      <c r="D160" s="22" t="inlineStr">
-        <is>
-          <t>2029/04/14</t>
-        </is>
-      </c>
+      <c r="D160" s="22" t="n"/>
       <c r="E160" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F160" s="23" t="inlineStr">
@@ -7305,7 +6941,7 @@
       </c>
       <c r="D161" s="22" t="inlineStr">
         <is>
-          <t>2029/04/21</t>
+          <t>2027/01/23</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
@@ -7392,14 +7028,10 @@
           <t>2026/09/14T09:07:14+09:00</t>
         </is>
       </c>
-      <c r="D162" s="22" t="inlineStr">
-        <is>
-          <t>2029/04/28</t>
-        </is>
-      </c>
+      <c r="D162" s="22" t="n"/>
       <c r="E162" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F162" s="23" t="inlineStr">
@@ -7467,7 +7099,7 @@
       </c>
       <c r="D163" s="22" t="inlineStr">
         <is>
-          <t>2029/05/05</t>
+          <t>2027/01/26</t>
         </is>
       </c>
       <c r="E163" s="23" t="inlineStr">
@@ -7550,7 +7182,7 @@
       </c>
       <c r="D164" s="22" t="inlineStr">
         <is>
-          <t>2029/05/12</t>
+          <t>2027/01/28</t>
         </is>
       </c>
       <c r="E164" s="23" t="inlineStr">
@@ -7619,14 +7251,10 @@
           <t>2026/09/25T09:06:26+09:00</t>
         </is>
       </c>
-      <c r="D165" s="22" t="inlineStr">
-        <is>
-          <t>2029/05/19</t>
-        </is>
-      </c>
+      <c r="D165" s="22" t="n"/>
       <c r="E165" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F165" s="23" t="inlineStr">
@@ -7694,7 +7322,7 @@
       </c>
       <c r="D166" s="22" t="inlineStr">
         <is>
-          <t>2029/05/26</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="E166" s="23" t="inlineStr">
@@ -7757,7 +7385,7 @@
       </c>
       <c r="D167" s="22" t="inlineStr">
         <is>
-          <t>2029/06/02</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="E167" s="23" t="inlineStr">
@@ -7852,14 +7480,10 @@
           <t>2026/10/02T09:06:01+09:00</t>
         </is>
       </c>
-      <c r="D168" s="22" t="inlineStr">
-        <is>
-          <t>2029/06/09</t>
-        </is>
-      </c>
+      <c r="D168" s="22" t="n"/>
       <c r="E168" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F168" s="23" t="inlineStr">
@@ -7916,14 +7540,10 @@
           <t>2026/10/03T09:05:07+09:00</t>
         </is>
       </c>
-      <c r="D169" s="22" t="inlineStr">
-        <is>
-          <t>2029/06/16</t>
-        </is>
-      </c>
+      <c r="D169" s="22" t="n"/>
       <c r="E169" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F169" s="23" t="inlineStr">
@@ -7981,14 +7601,10 @@
           <t>2026/10/09T09:07:31+09:00</t>
         </is>
       </c>
-      <c r="D170" s="22" t="inlineStr">
-        <is>
-          <t>2029/06/23</t>
-        </is>
-      </c>
+      <c r="D170" s="22" t="n"/>
       <c r="E170" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F170" s="23" t="inlineStr">
@@ -8049,7 +7665,7 @@
       </c>
       <c r="D171" s="22" t="inlineStr">
         <is>
-          <t>2029/06/30</t>
+          <t>2027/02/04</t>
         </is>
       </c>
       <c r="E171" s="23" t="inlineStr">
@@ -8128,7 +7744,7 @@
       <c r="C172" s="23" t="n"/>
       <c r="D172" s="22" t="inlineStr">
         <is>
-          <t>2029/07/07</t>
+          <t>2027/02/06</t>
         </is>
       </c>
       <c r="E172" s="23" t="inlineStr">
@@ -8203,7 +7819,7 @@
       <c r="C173" s="23" t="n"/>
       <c r="D173" s="22" t="inlineStr">
         <is>
-          <t>2029/07/14</t>
+          <t>2027/02/09</t>
         </is>
       </c>
       <c r="E173" s="23" t="inlineStr">
@@ -8282,14 +7898,10 @@
           <t>2026/09/26T16:32:42+09:00</t>
         </is>
       </c>
-      <c r="D174" s="22" t="inlineStr">
-        <is>
-          <t>2029/07/21</t>
-        </is>
-      </c>
+      <c r="D174" s="22" t="n"/>
       <c r="E174" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F174" s="23" t="inlineStr">
@@ -8372,14 +7984,10 @@
           <t>2026/09/28T12:26:54+09:00</t>
         </is>
       </c>
-      <c r="D175" s="22" t="inlineStr">
-        <is>
-          <t>2029/07/28</t>
-        </is>
-      </c>
+      <c r="D175" s="22" t="n"/>
       <c r="E175" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F175" s="23" t="inlineStr">
@@ -8444,7 +8052,7 @@
       <c r="C176" s="23" t="n"/>
       <c r="D176" s="22" t="inlineStr">
         <is>
-          <t>2029/08/04</t>
+          <t>2027/02/11</t>
         </is>
       </c>
       <c r="E176" s="23" t="inlineStr">
@@ -8542,7 +8150,7 @@
       <c r="C177" s="23" t="n"/>
       <c r="D177" s="22" t="inlineStr">
         <is>
-          <t>2029/08/11</t>
+          <t>2027/02/13</t>
         </is>
       </c>
       <c r="E177" s="23" t="inlineStr">
@@ -8610,14 +8218,10 @@
         </is>
       </c>
       <c r="C178" s="23" t="n"/>
-      <c r="D178" s="22" t="inlineStr">
-        <is>
-          <t>2029/08/18</t>
-        </is>
-      </c>
+      <c r="D178" s="22" t="n"/>
       <c r="E178" s="23" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>⏭ 見送り（選別）</t>
         </is>
       </c>
       <c r="F178" s="23" t="inlineStr">
@@ -8689,7 +8293,7 @@
       </c>
       <c r="D179" s="22" t="inlineStr">
         <is>
-          <t>2029/08/25</t>
+          <t>2027/02/16</t>
         </is>
       </c>
       <c r="E179" s="23" t="inlineStr">
@@ -8796,7 +8400,7 @@
       <c r="C180" s="23" t="n"/>
       <c r="D180" s="22" t="inlineStr">
         <is>
-          <t>2029/09/01</t>
+          <t>2027/02/18</t>
         </is>
       </c>
       <c r="E180" s="23" t="inlineStr">
@@ -8891,7 +8495,7 @@
       </c>
       <c r="D181" s="22" t="inlineStr">
         <is>
-          <t>2029/09/08</t>
+          <t>2027/02/20</t>
         </is>
       </c>
       <c r="E181" s="23" t="inlineStr">
@@ -8975,7 +8579,7 @@
       <c r="C182" s="23" t="n"/>
       <c r="D182" s="22" t="inlineStr">
         <is>
-          <t>2029/09/15</t>
+          <t>2027/02/23</t>
         </is>
       </c>
       <c r="E182" s="23" t="inlineStr">
@@ -9045,7 +8649,7 @@
       <c r="C183" s="23" t="n"/>
       <c r="D183" s="22" t="inlineStr">
         <is>
-          <t>2029/09/22</t>
+          <t>2027/02/25</t>
         </is>
       </c>
       <c r="E183" s="23" t="inlineStr">
@@ -9150,7 +8754,7 @@
       <c r="C184" s="23" t="n"/>
       <c r="D184" s="22" t="inlineStr">
         <is>
-          <t>2029/09/29</t>
+          <t>2027/02/27</t>
         </is>
       </c>
       <c r="E184" s="23" t="inlineStr">
@@ -9239,7 +8843,7 @@
       <c r="C185" s="23" t="n"/>
       <c r="D185" s="22" t="inlineStr">
         <is>
-          <t>2029/10/06</t>
+          <t>2027/03/02</t>
         </is>
       </c>
       <c r="E185" s="23" t="inlineStr">
@@ -9319,7 +8923,7 @@
       <c r="C186" s="23" t="n"/>
       <c r="D186" s="22" t="inlineStr">
         <is>
-          <t>2029/10/13</t>
+          <t>2027/03/04</t>
         </is>
       </c>
       <c r="E186" s="23" t="inlineStr">
@@ -9404,7 +9008,7 @@
       <c r="C187" s="23" t="n"/>
       <c r="D187" s="22" t="inlineStr">
         <is>
-          <t>2029/10/20</t>
+          <t>2027/03/06</t>
         </is>
       </c>
       <c r="E187" s="23" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>2026/10/27</t>
+          <t>2026/10/31</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>2026/10/29</t>
+          <t>2026/11/07</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>2026/10/31</t>
+          <t>2026/11/14</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>2026/11/03</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>2026/11/05</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>2026/11/07</t>
+          <t>2026/12/05</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>2026/11/10</t>
+          <t>2026/12/12</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>2026/11/12</t>
+          <t>2026/12/19</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>2026/11/14</t>
+          <t>2026/12/26</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>2026/11/17</t>
+          <t>2027/01/02</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D115" s="22" t="inlineStr">
         <is>
-          <t>2026/11/19</t>
+          <t>2027/01/09</t>
         </is>
       </c>
       <c r="E115" s="21" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D116" s="22" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2027/01/16</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="D118" s="22" t="inlineStr">
         <is>
-          <t>2026/11/24</t>
+          <t>2027/01/23</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="D120" s="22" t="inlineStr">
         <is>
-          <t>2026/11/26</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="D122" s="22" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/02/06</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="D123" s="22" t="inlineStr">
         <is>
-          <t>2026/12/01</t>
+          <t>2027/02/13</t>
         </is>
       </c>
       <c r="E123" s="21" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="D126" s="22" t="inlineStr">
         <is>
-          <t>2026/12/03</t>
+          <t>2027/02/20</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D127" s="22" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>2027/02/27</t>
         </is>
       </c>
       <c r="E127" s="21" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2027/03/06</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="D129" s="22" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>2027/03/13</t>
         </is>
       </c>
       <c r="E129" s="21" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D132" s="22" t="inlineStr">
         <is>
-          <t>2026/12/12</t>
+          <t>2027/03/20</t>
         </is>
       </c>
       <c r="E132" s="21" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="D134" s="22" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2027/03/27</t>
         </is>
       </c>
       <c r="E134" s="21" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>2026/12/17</t>
+          <t>2027/04/03</t>
         </is>
       </c>
       <c r="E137" s="21" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="D139" s="22" t="inlineStr">
         <is>
-          <t>2026/12/19</t>
+          <t>2027/04/10</t>
         </is>
       </c>
       <c r="E139" s="21" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="D141" s="22" t="inlineStr">
         <is>
-          <t>2026/12/22</t>
+          <t>2027/04/17</t>
         </is>
       </c>
       <c r="E141" s="21" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="D143" s="22" t="inlineStr">
         <is>
-          <t>2026/12/24</t>
+          <t>2027/04/24</t>
         </is>
       </c>
       <c r="E143" s="21" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="D144" s="22" t="inlineStr">
         <is>
-          <t>2026/12/26</t>
+          <t>2027/05/01</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="D145" s="22" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2027/05/08</t>
         </is>
       </c>
       <c r="E145" s="21" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D148" s="22" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/05/15</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D149" s="22" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/05/22</t>
         </is>
       </c>
       <c r="E149" s="21" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="D150" s="22" t="inlineStr">
         <is>
-          <t>2027/01/05</t>
+          <t>2027/05/29</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D153" s="22" t="inlineStr">
         <is>
-          <t>2027/01/07</t>
+          <t>2027/06/05</t>
         </is>
       </c>
       <c r="E153" s="21" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="D154" s="22" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>2027/06/12</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="D155" s="22" t="inlineStr">
         <is>
-          <t>2027/01/12</t>
+          <t>2027/06/19</t>
         </is>
       </c>
       <c r="E155" s="21" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="D156" s="22" t="inlineStr">
         <is>
-          <t>2027/01/14</t>
+          <t>2027/06/26</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="D157" s="22" t="inlineStr">
         <is>
-          <t>2027/01/16</t>
+          <t>2027/07/03</t>
         </is>
       </c>
       <c r="E157" s="21" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D158" s="22" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2027/07/10</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="D159" s="22" t="inlineStr">
         <is>
-          <t>2027/01/21</t>
+          <t>2027/07/17</t>
         </is>
       </c>
       <c r="E159" s="21" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="D161" s="22" t="inlineStr">
         <is>
-          <t>2027/01/23</t>
+          <t>2027/07/24</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="D163" s="22" t="inlineStr">
         <is>
-          <t>2027/01/26</t>
+          <t>2027/07/31</t>
         </is>
       </c>
       <c r="E163" s="23" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="D164" s="22" t="inlineStr">
         <is>
-          <t>2027/01/28</t>
+          <t>2027/08/07</t>
         </is>
       </c>
       <c r="E164" s="23" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D166" s="22" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2027/08/14</t>
         </is>
       </c>
       <c r="E166" s="23" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="D167" s="22" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/08/21</t>
         </is>
       </c>
       <c r="E167" s="23" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="D171" s="22" t="inlineStr">
         <is>
-          <t>2027/02/04</t>
+          <t>2027/08/28</t>
         </is>
       </c>
       <c r="E171" s="23" t="inlineStr">
@@ -7744,7 +7744,7 @@
       <c r="C172" s="23" t="n"/>
       <c r="D172" s="22" t="inlineStr">
         <is>
-          <t>2027/02/06</t>
+          <t>2027/09/04</t>
         </is>
       </c>
       <c r="E172" s="23" t="inlineStr">
@@ -7819,7 +7819,7 @@
       <c r="C173" s="23" t="n"/>
       <c r="D173" s="22" t="inlineStr">
         <is>
-          <t>2027/02/09</t>
+          <t>2027/09/11</t>
         </is>
       </c>
       <c r="E173" s="23" t="inlineStr">
@@ -8052,7 +8052,7 @@
       <c r="C176" s="23" t="n"/>
       <c r="D176" s="22" t="inlineStr">
         <is>
-          <t>2027/02/11</t>
+          <t>2027/09/18</t>
         </is>
       </c>
       <c r="E176" s="23" t="inlineStr">
@@ -8150,7 +8150,7 @@
       <c r="C177" s="23" t="n"/>
       <c r="D177" s="22" t="inlineStr">
         <is>
-          <t>2027/02/13</t>
+          <t>2027/09/25</t>
         </is>
       </c>
       <c r="E177" s="23" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="D179" s="22" t="inlineStr">
         <is>
-          <t>2027/02/16</t>
+          <t>2027/10/02</t>
         </is>
       </c>
       <c r="E179" s="23" t="inlineStr">
@@ -8400,7 +8400,7 @@
       <c r="C180" s="23" t="n"/>
       <c r="D180" s="22" t="inlineStr">
         <is>
-          <t>2027/02/18</t>
+          <t>2027/10/09</t>
         </is>
       </c>
       <c r="E180" s="23" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="D181" s="22" t="inlineStr">
         <is>
-          <t>2027/02/20</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="E181" s="23" t="inlineStr">
@@ -8579,7 +8579,7 @@
       <c r="C182" s="23" t="n"/>
       <c r="D182" s="22" t="inlineStr">
         <is>
-          <t>2027/02/23</t>
+          <t>2027/10/23</t>
         </is>
       </c>
       <c r="E182" s="23" t="inlineStr">
@@ -8649,7 +8649,7 @@
       <c r="C183" s="23" t="n"/>
       <c r="D183" s="22" t="inlineStr">
         <is>
-          <t>2027/02/25</t>
+          <t>2027/10/30</t>
         </is>
       </c>
       <c r="E183" s="23" t="inlineStr">
@@ -8754,7 +8754,7 @@
       <c r="C184" s="23" t="n"/>
       <c r="D184" s="22" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>2027/11/06</t>
         </is>
       </c>
       <c r="E184" s="23" t="inlineStr">
@@ -8843,7 +8843,7 @@
       <c r="C185" s="23" t="n"/>
       <c r="D185" s="22" t="inlineStr">
         <is>
-          <t>2027/03/02</t>
+          <t>2027/11/13</t>
         </is>
       </c>
       <c r="E185" s="23" t="inlineStr">
@@ -8923,7 +8923,7 @@
       <c r="C186" s="23" t="n"/>
       <c r="D186" s="22" t="inlineStr">
         <is>
-          <t>2027/03/04</t>
+          <t>2027/11/20</t>
         </is>
       </c>
       <c r="E186" s="23" t="inlineStr">
@@ -9008,7 +9008,7 @@
       <c r="C187" s="23" t="n"/>
       <c r="D187" s="22" t="inlineStr">
         <is>
-          <t>2027/03/06</t>
+          <t>2027/11/27</t>
         </is>
       </c>
       <c r="E187" s="23" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -48,7 +48,7 @@
       <color rgb="FF0A0A0A"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +91,16 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -112,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -175,6 +185,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8997,26 +9013,26 @@
       </c>
     </row>
     <row r="187" ht="15.75" customHeight="1" s="18">
-      <c r="A187" s="23" t="n">
+      <c r="A187" s="24" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="23" t="inlineStr">
+      <c r="B187" s="24" t="inlineStr">
         <is>
           <t>「じゃあ、もう一回頑張ってみる？」に大きく首を振る次男。計算カード1分29秒に悔し泣きした夜</t>
         </is>
       </c>
-      <c r="C187" s="23" t="n"/>
-      <c r="D187" s="22" t="inlineStr">
+      <c r="C187" s="24" t="n"/>
+      <c r="D187" s="25" t="inlineStr">
         <is>
           <t>2027/11/27</t>
         </is>
       </c>
-      <c r="E187" s="23" t="inlineStr">
+      <c r="E187" s="24" t="inlineStr">
         <is>
           <t>📝 予定</t>
         </is>
       </c>
-      <c r="F187" s="23" t="inlineStr">
+      <c r="F187" s="24" t="inlineStr">
         <is>
           <t>サッカーから帰ってぐったりの次男。
 寝る時間の夜8時から宿題と向き合った夜の話です😢

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -48,7 +48,7 @@
       <color rgb="FF0A0A0A"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +101,11 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5E8D4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -122,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -191,6 +196,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -468,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9113,7 +9121,95 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="15.75" customHeight="1" s="18"/>
+    <row r="188" ht="15.75" customHeight="1" s="18">
+      <c r="A188" s="26" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="26" t="inlineStr">
+        <is>
+          <t>「NO！」と大きな❌。15秒速くなったのにまた床を叩いた次男と、昨日との決定的な違い</t>
+        </is>
+      </c>
+      <c r="C188" s="26" t="n"/>
+      <c r="D188" s="25" t="inlineStr">
+        <is>
+          <t>2027/12/04</t>
+        </is>
+      </c>
+      <c r="E188" s="26" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F188" s="26" t="inlineStr">
+        <is>
+          <t>翌日の話です。デジャブかと思いました😂
+昨日、計算カードのタイムが悔しくて
+床を叩いて泣いた小1次男。
+今日のタイムは1分14秒。
+昨日より15秒速くなっていました✨
+【ただしカンニングは少ししていました】
+昨日は一度も見なかったのに
+今日は少し答えを見ていました。
+なので15秒のうち何秒かは「見た分」です。
+まぁ小1なんてそんなものです。
+昨日あれだけ泣いて今日も一度も見ずにやれたら
+それはもう小1ではありません😇
+【そしてまた床を叩いていました】
+目標の1分は切れず。
+同じ場所で、同じ姿勢で、同じように。
+昨日の映像をもう一度見ているようでした。
+【でも昨日とは3つ違いました】
+① 泣いている時間がすごく短かった
+② 気持ちの切り替えが早かった
+③ 明日の支度をすぐにできた
+昨日は泣いてそのまま寝ました。
+今日は泣いたあと自分で次の行動に移れました。
+【たぶん「昨日の今日」だったからです】
+昨日は泣いている理由を本人も言えず
+こちらから
+「タイムが遅かったから、悔しかった？」
+と聞いてようやく頷きました。
+そして今日、
+まったく同じ感情がもう一度やってきた。
+昨日もらった「悔しい」という言葉と
+今の自分の気持ちが結びついたのだと思います。
+これが1週間後だったら
+たぶんつながりませんでした。
+昨日の感情を覚えているうちに
+同じ感情が来たから
+「ああ、これがあれか」となった。
+以前こういう話を聞いたことがあります。
+気持ちと言葉が合致すると
+感情のコントロールがつきやすくなる。
+正体の分からないモヤモヤは扱いようがない。
+でも「これは悔しいという気持ちだ」と分かれば
+持て余す時間が短くなる。
+大人でも同じだと思います。
+【そして昨日と同じ質問をしてみました】
+「じゃあ、もう一回頑張ってみる？」
+被せ気味に「NO！」
+腕で大きな❌😂
+早い。食い気味です。
+昨日は首を振るだけでしたが
+今日は声と全身で来ました。
+うん、想定内！笑
+【1日で変わったのはタイムではなかった】
+変わったのは
+・泣いている時間
+・切り替えの早さ
+・そのあと自分で動けたこと
+悔しさとの付き合い方のほうでした。
+1分は切れていません。
+明日もたぶん切れません。
+でも昨日より今日のほうが立ち直りが早かった。
+それで十分だと思っています😊
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#小1 #3人育児 #子どもの成長 #計算カード #感情のコントロール #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="189" ht="15.75" customHeight="1" s="18"/>
     <row r="190" ht="15.75" customHeight="1" s="18"/>
     <row r="191" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -9193,6 +9193,12 @@
 早い。食い気味です。
 昨日は首を振るだけでしたが
 今日は声と全身で来ました。
+ちなみにこの「NO！」は発音がいいんです。
+カタカナの「ノー」ではなく、ちゃんと「NO！」。
+どこで覚えたのか分かりません😂
+拒否されているのに感心してしまいました。
+やる気は出ないのに発音だけは出る。
+何なんでしょうね。
 うん、想定内！笑
 【1日で変わったのはタイムではなかった】
 変わったのは

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9216,7 +9216,103 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="15.75" customHeight="1" s="18"/>
+    <row r="189" ht="15.75" customHeight="1" s="18">
+      <c r="A189" s="24" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="24" t="inlineStr">
+        <is>
+          <t>「音を外さない1年生は珍しい」と担任に言われた次男の耳。習っていない英語の歌まで発音よく歌います</t>
+        </is>
+      </c>
+      <c r="C189" s="24" t="n"/>
+      <c r="D189" s="25" t="inlineStr">
+        <is>
+          <t>2027/12/11</t>
+        </is>
+      </c>
+      <c r="E189" s="24" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F189" s="24" t="inlineStr">
+        <is>
+          <t>保護者面談で、思ってもみなかったことを
+言われました🎵
+「歌が上手いですよね。
+　音を外さずに、しっかり音を取れている
+　小学1年生は珍しいです」
+正直びっくりしました。
+家で歌っているのは聞いています。
+でも「珍しいこと」だとは思っていませんでした。
+親にとってはそれが普通なんですよね。
+生まれたときから聞いているので
+比べる相手がいません。
+【言われてみれば思い当たります】
+・字幕なしの英語のYouTubeを発音よく歌う
+　カタカナの「えーびーしー」ではなく
+　ちゃんと英語の音で出てきます
+・ロブロックスのキャラクター名も流暢
+　大人が読むと噛むような長い名前を
+　すらすら言います
+・「NO！」の発音までいい
+　計算カードを拒否したときの「NO！」が
+　カタカナの「ノー」じゃないんです😂
+【最初に気づいたのはトーマスのとき】
+映画の英語の歌を上手に歌っていました。
+そのときは「よく覚えたねー」くらいにしか
+思っていませんでしたが
+あれが最初のサインだったのかもしれません。
+意味が分からないものを音だけで再現している。
+【ピアノは習っています。でもこれは習っていません】
+次男は4歳からピアノを習っています。
+基礎はそこで身についたと思います。
+でも——
+・英語の歌は習っていません
+・発音も習っていません
+・イントネーションはなおさらです
+ピアノで習うのは
+楽譜を読んで鍵盤を押すこと。
+字幕のない英語のYouTubeを耳で拾って
+再現することは一度も教わっていません。
+それなのに、やっています。
+習ったことと、できていることがずれている。
+ここが面白いところです。
+たぶん入口が「耳」なんだと思います。
+意味は分からなくても音だけ先に入って
+そのまま出せる。
+【本人には自覚がありません】
+歌うのは楽しいから。
+真似るのはそう聞こえたから。
+努力している感覚がゼロなんです。
+できないことは本人がいちばん気づきます。
+漢字が書けない、タイムが遅い、宿題が終わらない。
+でも、できることは気づけません。
+自分にとっては当たり前だからです。
+【だから言葉にしていきたい】
+本人にも伝えました。
+「先生がね、歌が上手いって言ってたよ。
+　音を外さないんだって」
+「ふーん」という顔。
+ピンときていません😂
+それでいいと思っています。
+今は分からなくても
+「そう言われたことがある」という記憶だけ
+残れば十分です。
+できていないことは放っておいても気づきます。
+悔しくて泣くくらいですから。
+でも、できていることは
+誰かが言葉にしないと本人に届きません。
+「歌が上手いね」
+「その発音、どこで覚えたの？」
+そういう一言を忘れずに言っていきたいです😊
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#小1 #子どもの成長 #ピアノ #絶対音感 #保護者面談 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="190" ht="15.75" customHeight="1" s="18"/>
     <row r="191" ht="15.75" customHeight="1" s="18"/>
     <row r="192" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F190"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9313,7 +9313,100 @@
         </is>
       </c>
     </row>
-    <row r="190" ht="15.75" customHeight="1" s="18"/>
+    <row r="190" ht="15.75" customHeight="1" s="18">
+      <c r="A190" s="26" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="26" t="inlineStr">
+        <is>
+          <t>「一人3つだよ！」朝のウィンナーを即座に数える長女。小さい子順でも大きい子順でも、2番目です</t>
+        </is>
+      </c>
+      <c r="C190" s="26" t="n"/>
+      <c r="D190" s="25" t="inlineStr">
+        <is>
+          <t>2027/12/18</t>
+        </is>
+      </c>
+      <c r="E190" s="26" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F190" s="26" t="inlineStr">
+        <is>
+          <t>小4長女の「公平性」の話です🌭
+これ、毎日現れます。
+【朝のウィンナー】
+お皿に並べた瞬間、長女が一言。
+「一人3つだよ！」
+兄弟たちに指導が入ります。
+数えてから言っているのではありません。
+見た瞬間に数が分かっています。
+【お菓子は長女に分けさせます】
+分け方にとにかくうるさいので
+我が家ではこうしています。
+長女に分けさせて、最後に取らせる。
+分ける人が最後に取るとなると
+不公平に分けたら自分が損します。
+だから本気で均等に分けます。
+そして本人が「これでいい」と言うので
+誰からも文句が出ません。
+公平性にこだわる子を分ける係にする。
+これ、かなり効いています✨
+【どっち順でも、長女は2番目】
+テレビやゲームの順番でもひと悶着。
+・小さい子順（次男→長女→長男）
+・大きい子順（長男→長女→次男）
+気づきました。
+どっちでも長女は2番目です。
+3人きょうだいの真ん中なので
+どっちから数えても真ん中なんです。
+長男は「大きい子順」で1番になれる。
+次男は「小さい子順」で1番になれる。
+長女だけ、1番になる日がありません。
+構造的にどうやっても1番になれない。
+異議申し立ても当然でした。
+なので今は
+順番は子どもたちで話し合って決めています。
+【ただし自分のことは棚に上げます】
+自分だけ何か買ってもらうのは
+まったく問題を感じません。ニコニコです。
+ところが他の子が同じ状況だと知ったとたん
+「ずるい」
+……自分のときは何も言わなかったですよね😂
+見事に棚に上げています。
+でもこれが普通だと思います。小4です。
+むしろ自分が損したときに声を上げられるのは
+悪いことではありません。
+【お手伝いは「実行時間」で測ります】
+長女の中にははっきりした基準があります。
+実行時間が長い人がいちばん働いている。
+なので短時間で終わる人に厳しいです。
+でも名誉のために書いておきます。
+夏休みのお手伝い、長女は洗濯担当でした。
+干す→畳む→しまう。終わるまでが長いです。
+つまり長女の主張は正しかったのです。
+実際にいちばん働いていました。
+【本当は女王様でいたいのだと思います】
+公平性を主張しつつ
+本音では「私を立ててほしい」のだと思います。
+でも我が家はキャラが立っている人ばかり。
+長男と次男が黙って従うわけがありません。
+結果、いつも1対2。
+肩身の狭い思いをしていることも多いです。
+そしてここで登場するのがパパ。
+劣勢の長女にパパがつきます。
+女王と、舎弟。
+……我が家の力関係、そんな感じです😂
+というわけで今朝もウィンナーは3つずつ。
+誰も数え間違えていません。監査が入っているので。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#小4 #3人育児 #真ん中っ子 #きょうだい #子育て日記 #育児あるある #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="191" ht="15.75" customHeight="1" s="18"/>
     <row r="192" ht="15.75" customHeight="1" s="18"/>
     <row r="193" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7765,7 +7765,11 @@
           <t>楽天モバイルを3年使った正直な話。1回線8,000円が2,000円台になったけれど、困ることもあります</t>
         </is>
       </c>
-      <c r="C172" s="23" t="n"/>
+      <c r="C172" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/16T08:57:07+09:00</t>
+        </is>
+      </c>
       <c r="D172" s="22" t="inlineStr">
         <is>
           <t>2027/09/04</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -7844,7 +7844,11 @@
           <t>スマホが圏外で決済できない。地下のお店でクーポンが出せなかった日と、それからやっていること</t>
         </is>
       </c>
-      <c r="C173" s="23" t="n"/>
+      <c r="C173" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/17T09:09:09+09:00</t>
+        </is>
+      </c>
       <c r="D173" s="22" t="inlineStr">
         <is>
           <t>2027/09/11</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F190"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9415,7 +9415,115 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="15.75" customHeight="1" s="18"/>
+    <row r="191" ht="15.75" customHeight="1" s="18">
+      <c r="A191" s="24" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="24" t="inlineStr">
+        <is>
+          <t>「女王と舎弟」の正体が分かりました。家族4人で強みチェックをやったら、見事に全員バラバラだった話</t>
+        </is>
+      </c>
+      <c r="C191" s="24" t="n"/>
+      <c r="D191" s="25" t="inlineStr">
+        <is>
+          <t>2027/12/25</t>
+        </is>
+      </c>
+      <c r="E191" s="24" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F191" s="24" t="inlineStr">
+        <is>
+          <t>家族4人で「強みチェック」をやってみたら
+見事に全員バラバラでした😂
+夫・私・長男(小6)・長女(小4)の4人です。
+※正式な診断ではなく簡易的なセルフチェックです。
+　家族で話すきっかけとして楽しみました。
+【1位が全員違いました】
+私　　アレンジ
+夫　　調和性
+長男　社交性
+長女　公平性
+【4グループのバランス】
+　　　実行力 影響力 人間関係 戦略
+私　　 66%　 68%　 78%　 63%
+夫　　 68%　 51%　 66%　 74%
+長男　 33%　 78%　 58%　 72%
+長女　 57%　 62%　 66%　 47%
+誰かが高いところは誰かが低い。
+家族でちょうど補い合っているようにも見えます。
+【「女王と舎弟」の正体が分かりました】
+我が家には長女が女王でパパが舎弟という
+構図があります。
+長女が主張して、兄弟が黙っていなくて
+1対2になって、劣勢の長女にパパがつく。
+これ、数字で説明がつきました。
+・長女：指令性が2位（はっきり言う）
+・夫　：調和性が1位（対立を和らげる）
+さらに夫は影響力51%で4人中いちばん低い。
+主導権を取りにいくタイプではありません。
+いちばん主張する子の隣に
+いちばんぶつからない人がつく。
+これ以上ないくらい自然でした😂
+【長男の実行力33%】
+正直に書きます。4人の中で突出して低いです。
+・やることリストでいまだに声かけが必要
+・読書感想文を「今日やる」と言って1週間放置
+・朝5時半に起きてすぐゲームとYouTube
+数字がそのまま出ました。
+でも同時に影響力78%で4人中トップ。
+社交性は15点満点でした。
+宿題に向かう力は弱い。
+でも人と関わる力はずば抜けている。
+今まで「進まない」ほうばかり見ていましたが
+同じ子の中に78%の部分があるわけです。
+得意な場所が違うだけでした。
+【私はアレンジ15点満点】
+・大掃除をセクションに分けて1か所ずつ
+・子どもがいない2時間を狙って掃除
+・送迎の合間に洗濯を干す
+…心当たりしかありません😂
+そして4人を並べてみたら
+アレンジが上位だったのは私だけでした。
+自分にとって簡単なことは
+強みだと気づけないんですね。
+【この結果って変わるの？】
+気になったので調べました。
+・大人はわりと安定するそうです
+・子どもはかなり変わるそうです
+性格が安定してくるのは大人になってから。
+長男は小6、これから思春期です。
+2〜3年後にやったら別人のような結果が
+出ても驚きません。
+ただ、根っこは残って
+出し方が変わるのだと思います。
+長女の「不公平が目につく」性質は残る。
+でも出し方は変わっていくはず。
+今：「一人3つだよ！」と指導が入る
+数年後：揉めたときに間に入って整理する
+同じものが違う形で出る。
+1年後にもう一度やってみます📝
+【いちばん持ち帰れたこと】
+下位の資質は「弱点」ではなく
+「あまりエネルギーを使わない領域」。
+長男の実行力が低いのはサボりではなく
+そこで力が出にくいから。だから仕組みで補う。
+長女の公平性が高いのはうるさいのではなく
+そういう目を持っているから。
+だからお菓子を分ける係を任せる。
+得意なところに仕事を置く。
+苦手なところは仕組みで補う。
+ちなみに次男(小1)は質問の理解が難しいので
+まだやっていません😊
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#強み #家族 #3人育児 #子育て日記 #夫婦 #自己理解 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="192" ht="15.75" customHeight="1" s="18"/>
     <row r="193" ht="15.75" customHeight="1" s="18"/>
     <row r="194" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -1913,7 +1913,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>2026/10/24</t>
+          <t>2026/10/31</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>2026/10/31</t>
+          <t>2026/11/07</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>2026/11/07</t>
+          <t>2026/11/14</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>2026/11/14</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2026/12/05</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>2026/12/12</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>2026/12/12</t>
+          <t>2026/12/19</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>2026/12/19</t>
+          <t>2026/12/26</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>2026/12/26</t>
+          <t>2027/01/02</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/09</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D115" s="22" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>2027/01/16</t>
         </is>
       </c>
       <c r="E115" s="21" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D116" s="22" t="inlineStr">
         <is>
-          <t>2027/01/16</t>
+          <t>2027/01/23</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="D118" s="22" t="inlineStr">
         <is>
-          <t>2027/01/23</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D120" s="22" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2027/02/06</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="D122" s="22" t="inlineStr">
         <is>
-          <t>2027/02/06</t>
+          <t>2027/02/13</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="D123" s="22" t="inlineStr">
         <is>
-          <t>2027/02/13</t>
+          <t>2027/02/20</t>
         </is>
       </c>
       <c r="E123" s="21" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="D126" s="22" t="inlineStr">
         <is>
-          <t>2027/02/20</t>
+          <t>2027/02/27</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="D127" s="22" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>2027/03/06</t>
         </is>
       </c>
       <c r="E127" s="21" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>2027/03/06</t>
+          <t>2027/03/13</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="D129" s="22" t="inlineStr">
         <is>
-          <t>2027/03/13</t>
+          <t>2027/03/20</t>
         </is>
       </c>
       <c r="E129" s="21" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="D132" s="22" t="inlineStr">
         <is>
-          <t>2027/03/20</t>
+          <t>2027/03/27</t>
         </is>
       </c>
       <c r="E132" s="21" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D134" s="22" t="inlineStr">
         <is>
-          <t>2027/03/27</t>
+          <t>2027/04/03</t>
         </is>
       </c>
       <c r="E134" s="21" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>2027/04/03</t>
+          <t>2027/04/10</t>
         </is>
       </c>
       <c r="E137" s="21" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="D139" s="22" t="inlineStr">
         <is>
-          <t>2027/04/10</t>
+          <t>2027/04/17</t>
         </is>
       </c>
       <c r="E139" s="21" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="D141" s="22" t="inlineStr">
         <is>
-          <t>2027/04/17</t>
+          <t>2027/04/24</t>
         </is>
       </c>
       <c r="E141" s="21" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="D143" s="22" t="inlineStr">
         <is>
-          <t>2027/04/24</t>
+          <t>2027/05/01</t>
         </is>
       </c>
       <c r="E143" s="21" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D144" s="22" t="inlineStr">
         <is>
-          <t>2027/05/01</t>
+          <t>2027/05/08</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="D145" s="22" t="inlineStr">
         <is>
-          <t>2027/05/08</t>
+          <t>2027/05/15</t>
         </is>
       </c>
       <c r="E145" s="21" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="D148" s="22" t="inlineStr">
         <is>
-          <t>2027/05/15</t>
+          <t>2027/05/22</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="D149" s="22" t="inlineStr">
         <is>
-          <t>2027/05/22</t>
+          <t>2027/05/29</t>
         </is>
       </c>
       <c r="E149" s="21" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="D150" s="22" t="inlineStr">
         <is>
-          <t>2027/05/29</t>
+          <t>2027/06/05</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="D153" s="22" t="inlineStr">
         <is>
-          <t>2027/06/05</t>
+          <t>2027/06/12</t>
         </is>
       </c>
       <c r="E153" s="21" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="D154" s="22" t="inlineStr">
         <is>
-          <t>2027/06/12</t>
+          <t>2027/06/19</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="D155" s="22" t="inlineStr">
         <is>
-          <t>2027/06/19</t>
+          <t>2027/06/26</t>
         </is>
       </c>
       <c r="E155" s="21" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D156" s="22" t="inlineStr">
         <is>
-          <t>2027/06/26</t>
+          <t>2027/07/03</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="D157" s="22" t="inlineStr">
         <is>
-          <t>2027/07/03</t>
+          <t>2027/07/10</t>
         </is>
       </c>
       <c r="E157" s="21" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="D158" s="22" t="inlineStr">
         <is>
-          <t>2027/07/10</t>
+          <t>2027/07/17</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="D159" s="22" t="inlineStr">
         <is>
-          <t>2027/07/17</t>
+          <t>2027/07/24</t>
         </is>
       </c>
       <c r="E159" s="21" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D161" s="22" t="inlineStr">
         <is>
-          <t>2027/07/24</t>
+          <t>2027/07/31</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D163" s="22" t="inlineStr">
         <is>
-          <t>2027/07/31</t>
+          <t>2027/08/07</t>
         </is>
       </c>
       <c r="E163" s="23" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="D164" s="22" t="inlineStr">
         <is>
-          <t>2027/08/07</t>
+          <t>2027/08/14</t>
         </is>
       </c>
       <c r="E164" s="23" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D166" s="22" t="inlineStr">
         <is>
-          <t>2027/08/14</t>
+          <t>2027/08/21</t>
         </is>
       </c>
       <c r="E166" s="23" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D167" s="22" t="inlineStr">
         <is>
-          <t>2027/08/21</t>
+          <t>2027/08/28</t>
         </is>
       </c>
       <c r="E167" s="23" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D171" s="22" t="inlineStr">
         <is>
-          <t>2027/08/28</t>
+          <t>2027/09/04</t>
         </is>
       </c>
       <c r="E171" s="23" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D172" s="22" t="inlineStr">
         <is>
-          <t>2027/09/04</t>
+          <t>2027/09/11</t>
         </is>
       </c>
       <c r="E172" s="23" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D173" s="22" t="inlineStr">
         <is>
-          <t>2027/09/11</t>
+          <t>2027/09/18</t>
         </is>
       </c>
       <c r="E173" s="23" t="inlineStr">
@@ -8084,7 +8084,7 @@
       <c r="C176" s="23" t="n"/>
       <c r="D176" s="22" t="inlineStr">
         <is>
-          <t>2027/09/18</t>
+          <t>2027/09/25</t>
         </is>
       </c>
       <c r="E176" s="23" t="inlineStr">
@@ -8182,7 +8182,7 @@
       <c r="C177" s="23" t="n"/>
       <c r="D177" s="22" t="inlineStr">
         <is>
-          <t>2027/09/25</t>
+          <t>2027/10/02</t>
         </is>
       </c>
       <c r="E177" s="23" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="D179" s="22" t="inlineStr">
         <is>
-          <t>2027/10/02</t>
+          <t>2027/10/09</t>
         </is>
       </c>
       <c r="E179" s="23" t="inlineStr">
@@ -8432,7 +8432,7 @@
       <c r="C180" s="23" t="n"/>
       <c r="D180" s="22" t="inlineStr">
         <is>
-          <t>2027/10/09</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="E180" s="23" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D181" s="22" t="inlineStr">
         <is>
-          <t>2027/10/16</t>
+          <t>2027/10/23</t>
         </is>
       </c>
       <c r="E181" s="23" t="inlineStr">
@@ -8611,7 +8611,7 @@
       <c r="C182" s="23" t="n"/>
       <c r="D182" s="22" t="inlineStr">
         <is>
-          <t>2027/10/23</t>
+          <t>2027/10/30</t>
         </is>
       </c>
       <c r="E182" s="23" t="inlineStr">
@@ -8681,7 +8681,7 @@
       <c r="C183" s="23" t="n"/>
       <c r="D183" s="22" t="inlineStr">
         <is>
-          <t>2027/10/30</t>
+          <t>2027/11/06</t>
         </is>
       </c>
       <c r="E183" s="23" t="inlineStr">
@@ -8786,7 +8786,7 @@
       <c r="C184" s="23" t="n"/>
       <c r="D184" s="22" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2027/11/13</t>
         </is>
       </c>
       <c r="E184" s="23" t="inlineStr">
@@ -8875,7 +8875,7 @@
       <c r="C185" s="23" t="n"/>
       <c r="D185" s="22" t="inlineStr">
         <is>
-          <t>2027/11/13</t>
+          <t>2027/11/20</t>
         </is>
       </c>
       <c r="E185" s="23" t="inlineStr">
@@ -8955,7 +8955,7 @@
       <c r="C186" s="23" t="n"/>
       <c r="D186" s="22" t="inlineStr">
         <is>
-          <t>2027/11/20</t>
+          <t>2027/11/27</t>
         </is>
       </c>
       <c r="E186" s="23" t="inlineStr">
@@ -9040,7 +9040,7 @@
       <c r="C187" s="24" t="n"/>
       <c r="D187" s="25" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2027/12/04</t>
         </is>
       </c>
       <c r="E187" s="24" t="inlineStr">
@@ -9141,7 +9141,7 @@
       <c r="C188" s="26" t="n"/>
       <c r="D188" s="25" t="inlineStr">
         <is>
-          <t>2027/12/04</t>
+          <t>2027/12/11</t>
         </is>
       </c>
       <c r="E188" s="26" t="inlineStr">
@@ -9236,7 +9236,7 @@
       <c r="C189" s="24" t="n"/>
       <c r="D189" s="25" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2027/12/18</t>
         </is>
       </c>
       <c r="E189" s="24" t="inlineStr">
@@ -9333,7 +9333,7 @@
       <c r="C190" s="26" t="n"/>
       <c r="D190" s="25" t="inlineStr">
         <is>
-          <t>2027/12/18</t>
+          <t>2027/12/25</t>
         </is>
       </c>
       <c r="E190" s="26" t="inlineStr">
@@ -9427,7 +9427,7 @@
       <c r="C191" s="24" t="n"/>
       <c r="D191" s="25" t="inlineStr">
         <is>
-          <t>2027/12/25</t>
+          <t>2028/01/01</t>
         </is>
       </c>
       <c r="E191" s="24" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -1913,7 +1913,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>2026/10/31</t>
+          <t>2026/10/24</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>2026/11/07</t>
+          <t>2026/10/31</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>2026/11/14</t>
+          <t>2026/11/07</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/14</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
-          <t>2026/12/12</t>
+          <t>2026/12/05</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
-          <t>2026/12/19</t>
+          <t>2026/12/12</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>2026/12/26</t>
+          <t>2026/12/19</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2026/12/26</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>2027/01/02</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D115" s="22" t="inlineStr">
         <is>
-          <t>2027/01/16</t>
+          <t>2027/01/09</t>
         </is>
       </c>
       <c r="E115" s="21" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D116" s="22" t="inlineStr">
         <is>
-          <t>2027/01/23</t>
+          <t>2027/01/16</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="D118" s="22" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2027/01/23</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D120" s="22" t="inlineStr">
         <is>
-          <t>2027/02/06</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="D122" s="22" t="inlineStr">
         <is>
-          <t>2027/02/13</t>
+          <t>2027/02/06</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="D123" s="22" t="inlineStr">
         <is>
-          <t>2027/02/20</t>
+          <t>2027/02/13</t>
         </is>
       </c>
       <c r="E123" s="21" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="D126" s="22" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>2027/02/20</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="D127" s="22" t="inlineStr">
         <is>
-          <t>2027/03/06</t>
+          <t>2027/02/27</t>
         </is>
       </c>
       <c r="E127" s="21" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>2027/03/13</t>
+          <t>2027/03/06</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="D129" s="22" t="inlineStr">
         <is>
-          <t>2027/03/20</t>
+          <t>2027/03/13</t>
         </is>
       </c>
       <c r="E129" s="21" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="D132" s="22" t="inlineStr">
         <is>
-          <t>2027/03/27</t>
+          <t>2027/03/20</t>
         </is>
       </c>
       <c r="E132" s="21" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D134" s="22" t="inlineStr">
         <is>
-          <t>2027/04/03</t>
+          <t>2027/03/27</t>
         </is>
       </c>
       <c r="E134" s="21" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>2027/04/10</t>
+          <t>2027/04/03</t>
         </is>
       </c>
       <c r="E137" s="21" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="D139" s="22" t="inlineStr">
         <is>
-          <t>2027/04/17</t>
+          <t>2027/04/10</t>
         </is>
       </c>
       <c r="E139" s="21" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="D141" s="22" t="inlineStr">
         <is>
-          <t>2027/04/24</t>
+          <t>2027/04/17</t>
         </is>
       </c>
       <c r="E141" s="21" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="D143" s="22" t="inlineStr">
         <is>
-          <t>2027/05/01</t>
+          <t>2027/04/24</t>
         </is>
       </c>
       <c r="E143" s="21" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D144" s="22" t="inlineStr">
         <is>
-          <t>2027/05/08</t>
+          <t>2027/05/01</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="D145" s="22" t="inlineStr">
         <is>
-          <t>2027/05/15</t>
+          <t>2027/05/08</t>
         </is>
       </c>
       <c r="E145" s="21" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="D148" s="22" t="inlineStr">
         <is>
-          <t>2027/05/22</t>
+          <t>2027/05/15</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="D149" s="22" t="inlineStr">
         <is>
-          <t>2027/05/29</t>
+          <t>2027/05/22</t>
         </is>
       </c>
       <c r="E149" s="21" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="D150" s="22" t="inlineStr">
         <is>
-          <t>2027/06/05</t>
+          <t>2027/05/29</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="D153" s="22" t="inlineStr">
         <is>
-          <t>2027/06/12</t>
+          <t>2027/06/05</t>
         </is>
       </c>
       <c r="E153" s="21" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="D154" s="22" t="inlineStr">
         <is>
-          <t>2027/06/19</t>
+          <t>2027/06/12</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="D155" s="22" t="inlineStr">
         <is>
-          <t>2027/06/26</t>
+          <t>2027/06/19</t>
         </is>
       </c>
       <c r="E155" s="21" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D156" s="22" t="inlineStr">
         <is>
-          <t>2027/07/03</t>
+          <t>2027/06/26</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="D157" s="22" t="inlineStr">
         <is>
-          <t>2027/07/10</t>
+          <t>2027/07/03</t>
         </is>
       </c>
       <c r="E157" s="21" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="D158" s="22" t="inlineStr">
         <is>
-          <t>2027/07/17</t>
+          <t>2027/07/10</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="D159" s="22" t="inlineStr">
         <is>
-          <t>2027/07/24</t>
+          <t>2027/07/17</t>
         </is>
       </c>
       <c r="E159" s="21" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D161" s="22" t="inlineStr">
         <is>
-          <t>2027/07/31</t>
+          <t>2027/07/24</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D163" s="22" t="inlineStr">
         <is>
-          <t>2027/08/07</t>
+          <t>2027/07/31</t>
         </is>
       </c>
       <c r="E163" s="23" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="D164" s="22" t="inlineStr">
         <is>
-          <t>2027/08/14</t>
+          <t>2027/08/07</t>
         </is>
       </c>
       <c r="E164" s="23" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D166" s="22" t="inlineStr">
         <is>
-          <t>2027/08/21</t>
+          <t>2027/08/14</t>
         </is>
       </c>
       <c r="E166" s="23" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D167" s="22" t="inlineStr">
         <is>
-          <t>2027/08/28</t>
+          <t>2027/08/21</t>
         </is>
       </c>
       <c r="E167" s="23" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D171" s="22" t="inlineStr">
         <is>
-          <t>2027/09/04</t>
+          <t>2027/08/28</t>
         </is>
       </c>
       <c r="E171" s="23" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D172" s="22" t="inlineStr">
         <is>
-          <t>2027/09/11</t>
+          <t>2027/09/04</t>
         </is>
       </c>
       <c r="E172" s="23" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D173" s="22" t="inlineStr">
         <is>
-          <t>2027/09/18</t>
+          <t>2027/09/11</t>
         </is>
       </c>
       <c r="E173" s="23" t="inlineStr">
@@ -8084,7 +8084,7 @@
       <c r="C176" s="23" t="n"/>
       <c r="D176" s="22" t="inlineStr">
         <is>
-          <t>2027/09/25</t>
+          <t>2027/09/18</t>
         </is>
       </c>
       <c r="E176" s="23" t="inlineStr">
@@ -8182,7 +8182,7 @@
       <c r="C177" s="23" t="n"/>
       <c r="D177" s="22" t="inlineStr">
         <is>
-          <t>2027/10/02</t>
+          <t>2027/09/25</t>
         </is>
       </c>
       <c r="E177" s="23" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="D179" s="22" t="inlineStr">
         <is>
-          <t>2027/10/09</t>
+          <t>2027/10/02</t>
         </is>
       </c>
       <c r="E179" s="23" t="inlineStr">
@@ -8432,7 +8432,7 @@
       <c r="C180" s="23" t="n"/>
       <c r="D180" s="22" t="inlineStr">
         <is>
-          <t>2027/10/16</t>
+          <t>2027/10/09</t>
         </is>
       </c>
       <c r="E180" s="23" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D181" s="22" t="inlineStr">
         <is>
-          <t>2027/10/23</t>
+          <t>2027/10/16</t>
         </is>
       </c>
       <c r="E181" s="23" t="inlineStr">
@@ -8611,7 +8611,7 @@
       <c r="C182" s="23" t="n"/>
       <c r="D182" s="22" t="inlineStr">
         <is>
-          <t>2027/10/30</t>
+          <t>2027/10/23</t>
         </is>
       </c>
       <c r="E182" s="23" t="inlineStr">
@@ -8681,7 +8681,7 @@
       <c r="C183" s="23" t="n"/>
       <c r="D183" s="22" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2027/10/30</t>
         </is>
       </c>
       <c r="E183" s="23" t="inlineStr">
@@ -8786,7 +8786,7 @@
       <c r="C184" s="23" t="n"/>
       <c r="D184" s="22" t="inlineStr">
         <is>
-          <t>2027/11/13</t>
+          <t>2027/11/06</t>
         </is>
       </c>
       <c r="E184" s="23" t="inlineStr">
@@ -8875,7 +8875,7 @@
       <c r="C185" s="23" t="n"/>
       <c r="D185" s="22" t="inlineStr">
         <is>
-          <t>2027/11/20</t>
+          <t>2027/11/13</t>
         </is>
       </c>
       <c r="E185" s="23" t="inlineStr">
@@ -8955,7 +8955,7 @@
       <c r="C186" s="23" t="n"/>
       <c r="D186" s="22" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2027/11/20</t>
         </is>
       </c>
       <c r="E186" s="23" t="inlineStr">
@@ -9040,7 +9040,7 @@
       <c r="C187" s="24" t="n"/>
       <c r="D187" s="25" t="inlineStr">
         <is>
-          <t>2027/12/04</t>
+          <t>2027/11/27</t>
         </is>
       </c>
       <c r="E187" s="24" t="inlineStr">
@@ -9141,7 +9141,7 @@
       <c r="C188" s="26" t="n"/>
       <c r="D188" s="25" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2027/12/04</t>
         </is>
       </c>
       <c r="E188" s="26" t="inlineStr">
@@ -9236,7 +9236,7 @@
       <c r="C189" s="24" t="n"/>
       <c r="D189" s="25" t="inlineStr">
         <is>
-          <t>2027/12/18</t>
+          <t>2027/12/11</t>
         </is>
       </c>
       <c r="E189" s="24" t="inlineStr">
@@ -9333,7 +9333,7 @@
       <c r="C190" s="26" t="n"/>
       <c r="D190" s="25" t="inlineStr">
         <is>
-          <t>2027/12/25</t>
+          <t>2027/12/18</t>
         </is>
       </c>
       <c r="E190" s="26" t="inlineStr">
@@ -9427,7 +9427,7 @@
       <c r="C191" s="24" t="n"/>
       <c r="D191" s="25" t="inlineStr">
         <is>
-          <t>2028/01/01</t>
+          <t>2027/12/25</t>
         </is>
       </c>
       <c r="E191" s="24" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8608,7 +8608,11 @@
           <t>使っていない口座を解約したら、銀行印を紛失しかけて、最後に埋蔵金が出てきた話</t>
         </is>
       </c>
-      <c r="C182" s="23" t="n"/>
+      <c r="C182" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/19T08:57:46+09:00</t>
+        </is>
+      </c>
       <c r="D182" s="22" t="inlineStr">
         <is>
           <t>2027/10/23</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8682,7 +8682,11 @@
           <t>子どもがいない2時間が勝負。カーテン洗濯もリビングの床拭きも、10時前に終わりました</t>
         </is>
       </c>
-      <c r="C183" s="23" t="n"/>
+      <c r="C183" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/21T09:07:20+09:00</t>
+        </is>
+      </c>
       <c r="D183" s="22" t="inlineStr">
         <is>
           <t>2027/10/30</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9532,7 +9532,87 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="15.75" customHeight="1" s="18"/>
+    <row r="192" ht="15.75" customHeight="1" s="18">
+      <c r="A192" s="26" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="26" t="inlineStr">
+        <is>
+          <t>「俺踊る！」一度も練習しなかった次男と、「横断中」の旗で練習する長男。運動会前の我が家です</t>
+        </is>
+      </c>
+      <c r="C192" s="26" t="n"/>
+      <c r="D192" s="25" t="inlineStr">
+        <is>
+          <t>2028/01/01</t>
+        </is>
+      </c>
+      <c r="E192" s="26" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F192" s="26" t="inlineStr">
+        <is>
+          <t>今週末は子どもたちの運動会🏃
+ここ数日、家の中が練習場になっています。
+そして3人のやり方がまるで違いました。
+【長女：もはやアイドル】
+「バイバイファイト」でダンス。
+鏡の前で何度も確認して
+振りを細かく直して、曲をかけ直して、また踊る。
+本番より気合が入っているのでは…というくらい
+真剣にやっています✨
+ただ、ひとつ不思議なことが。
+運動会とまったく関係ない
+アイリットの「イッツミー」も
+たくさん練習しています。
+なぜ。謎です😂
+本番の曲より踊っている時間が長い気がします。
+【長男：フラッグが家にない】
+嵐の「ファイブ」でフラッグの演技。
+練習は……そこそこです。
+当然ですが演技用のフラッグは家にありません。
+そこで代用に選んだのが——
+旗振り当番の「横断中」の黄色い旗。
+朝、子どもたちを見送るときに使う、あれです。
+あの旗、振り回すものではありません。
+交差点で静かに掲げるためのものです。
+それを嵐の曲に合わせて全力で振り回した結果
+旗がスポーンと飛んでいきました😇
+しかも部品がなくなるという事件に。
+家族総出で探して、無事回収。組み直して元通り。
+次の旗振り当番のとき
+「横断中」は何事もなかったかのように
+子どもたちを見送ってくれると思います。
+…誰も知らない、あの数分間のことは。
+【次男：家で一度も練習していません】
+MILKの「爆裂愛してる」でダンス。
+家での練習は、一度もなし。一回も。
+ところが昨日、何の前触れもなく
+「俺踊る！」
+そして踊りました。完璧に。
+振りも大きく、全力で
+一度も間違えずに最後まで踊り切りました。
+学校の練習だけで全部入っていたということです。
+この子、一度入ったものをそのまま出せるんですよね。
+【3人3様でした】
+長女　練習：熱心（＋関係ない曲も）→ アイドル
+長男　練習：そこそこ（＋旗が飛ぶ）→ そこそこ
+次男　練習：ゼロ → 完璧
+同じ家で同じように育てているのに
+やり方がまったく違います。
+全部ちがう。でも全部、本人なりにやっている。
+本番がどうなるかは分かりませんが
+ここまでの数日間がすでに面白かったです😊
+実は先日まで風邪で喉をやられていました。
+運動会に向けて、私も体調を整えます💪
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#運動会 #3人育児 #小学生ママ #育児あるある #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="193" ht="15.75" customHeight="1" s="18"/>
     <row r="194" ht="15.75" customHeight="1" s="18"/>
     <row r="195" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -9607,6 +9607,8 @@
 ここまでの数日間がすでに面白かったです😊
 実は先日まで風邪で喉をやられていました。
 運動会に向けて、私も体調を整えます💪
+ちなみに午前中で終わるのでお弁当はありません。
+これは正直かなり助かります🙏
 ▶️ 続きはプロフィールのブログへ！
 https://3nin-dotabata.com
 #運動会 #3人育児 #小学生ママ #育児あるある #子育て日記 #ドタバタ母さん</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -9565,12 +9565,12 @@
 真剣にやっています✨
 ただ、ひとつ不思議なことが。
 運動会とまったく関係ない
-アイリットの「イッツミー」も
+ILLIT（アイリット）の「It's Me」も
 たくさん練習しています。
 なぜ。謎です😂
 本番の曲より踊っている時間が長い気がします。
 【長男：フラッグが家にない】
-嵐の「ファイブ」でフラッグの演技。
+嵐の「Five」でフラッグの演技。
 練習は……そこそこです。
 当然ですが演技用のフラッグは家にありません。
 そこで代用に選んだのが——
@@ -9587,7 +9587,7 @@
 子どもたちを見送ってくれると思います。
 …誰も知らない、あの数分間のことは。
 【次男：家で一度も練習していません】
-MILKの「爆裂愛してる」でダンス。
+M!LK（ミルク）の「爆裂愛してる」でダンス。
 家での練習は、一度もなし。一回も。
 ところが昨日、何の前触れもなく
 「俺踊る！」

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -9558,7 +9558,10 @@
 ここ数日、家の中が練習場になっています。
 そして3人のやり方がまるで違いました。
 【長女：もはやアイドル】
-「バイバイファイト」でダンス。
+CANDY TUNE（キャンディーチューン）の
+「倍倍FIGHT!」でダンス。
+「倍倍」と書いて「バイバイ」と読みます。
+しばらくカタカナだと思っていました😅
 鏡の前で何度も確認して
 振りを細かく直して、曲をかけ直して、また踊る。
 本番より気合が入っているのでは…というくらい

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -9554,7 +9554,8 @@
       </c>
       <c r="F192" s="26" t="inlineStr">
         <is>
-          <t>今週末は子どもたちの運動会🏃
+          <t>来週の水曜は子どもたちの運動会🏃
+（今週末の予定でしたが雨で延期になりました）
 ここ数日、家の中が練習場になっています。
 そして3人のやり方がまるで違いました。
 【長女：もはやアイドル】

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -9541,7 +9541,11 @@
           <t>「俺踊る！」一度も練習しなかった次男と、「横断中」の旗で練習する長男。運動会前の我が家です</t>
         </is>
       </c>
-      <c r="C192" s="26" t="n"/>
+      <c r="C192" s="26" t="inlineStr">
+        <is>
+          <t>2026/10/23T09:03:43+09:00</t>
+        </is>
+      </c>
       <c r="D192" s="25" t="inlineStr">
         <is>
           <t>2028/01/01</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8179,7 +8179,11 @@
           <t>毎晩数分の音読を2か月続けたら、驚くほど上手になりました。おまけに字まで</t>
         </is>
       </c>
-      <c r="C177" s="23" t="n"/>
+      <c r="C177" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/24T09:07:51+09:00</t>
+        </is>
+      </c>
       <c r="D177" s="22" t="inlineStr">
         <is>
           <t>2027/09/25</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9627,7 +9627,104 @@
         </is>
       </c>
     </row>
-    <row r="193" ht="15.75" customHeight="1" s="18"/>
+    <row r="193" ht="15.75" customHeight="1" s="18">
+      <c r="A193" s="24" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="24" t="inlineStr">
+        <is>
+          <t>体を洗う古いナイロンタオルが、網戸掃除に抜群でした。気分が沈んだ朝の小掃除4回目</t>
+        </is>
+      </c>
+      <c r="C193" s="24" t="n"/>
+      <c r="D193" s="25" t="inlineStr">
+        <is>
+          <t>2028/01/08</t>
+        </is>
+      </c>
+      <c r="E193" s="24" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F193" s="24" t="inlineStr">
+        <is>
+          <t>小掃除4回目は窓拭きです🪟
+1回目の記事で
+「冬の寒い中、窓拭きなんてやりたくありません」
+と書いていた、あれです。
+やっと取りかかれました。
+【その日の朝は、気分が沈んでいました】
+正直に書きます。
+なんだかうつうつとした気分でした。
+理由はひとつではありません。
+いろいろあって、なんとなく重い。
+こういう日は、たいてい何も進みません。
+【まず30分だけ散歩に出ました】
+掃除の前に、雨が降る前に30分ほど散歩へ。
+掃除をしに行ったわけではなく、ただ歩きに。
+戻ってきたとき、気分が少し軽くなっていました。
+動けない気分のときに
+いきなり掃除を始めるのは無理です。
+でも、歩くだけなら始められます。
+【8時前から9時まで】
+・窓拭き
+・網戸拭き
+・サッシの掃除
+・ベランダの整理
+約1時間で終わりました。
+【網戸には古いナイロンタオルが抜群】
+体を洗う、古くなったナイロンタオル。
+あれが網戸の汚れ落としに抜群でした✨
+なぜいいのか、理屈は分かっていません。
+やってみたら落ちた、というだけです。
+たぶん網戸の小さな隙間の汚れを
+かき出してくれているのかな、と思っています。
+あくまで推測です。
+調べてみたら、網戸掃除の定番として
+「使わなくなったストッキングに古布を詰めて
+丸めたもの」でなぞる方法がありました。
+ナイロンタオルは出てきませんでしたが
+発想は近い気がします。
+※網は強くこすると傷みます。
+　軽くなでる程度で十分落ちました。
+ナイロンタオルって、へたったら捨てますよね。
+その前に網戸に使ってみてください。
+【雨なのに明るくなりました】
+終わったあと、外は雨。
+それなのに部屋が明るくなった感じがしました。
+網戸の汚れって
+気づかないうちに光を遮っているんですね。
+【気分が沈んだ日こそ、掃除がよかった】
+① 結果が目に見える
+　落ち込んでいると何をやっても手応えがないけれど
+　掃除はやった分だけ確実にきれいになります
+② 考えなくていい
+　手を動かしているあいだは余計なことを考えません
+③ 1時間で終わる
+　終わりが決まっているから始められます
+【ここまでの小掃除】
+1 和室　　　　　　　　　1時間半
+2 カーテン・床拭き・棚　1時間45分
+3 救急箱・薬箱・チェスト 1時間弱
+4 窓・網戸・サッシ　　　1時間
+全部、午前中に終わっています。
+年末に残っているのは水回りくらいになってきました。
+【最後に、散歩のこと】
+掃除の前に30分歩いた。
+これがなければ、たぶんその日は何もできていません。
+やる気が出ないとき
+「やる気を出そう」としても出ません。
+でも歩くだけなら、やる気がなくてもできます。
+順番が逆なんですよね。
+やる気が出たから動くのではなく
+動いたからやる気が出る😊
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#小掃除 #大掃除 #窓拭き #網戸掃除 #暮らしの工夫 #掃除のコツ #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="194" ht="15.75" customHeight="1" s="18"/>
     <row r="195" ht="15.75" customHeight="1" s="18"/>
     <row r="196" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8795,7 +8795,11 @@
           <t>救急箱と薬箱を整理したら、使わない薬だらけでした。訪問看護師が残したもの・捨てたもの</t>
         </is>
       </c>
-      <c r="C184" s="23" t="n"/>
+      <c r="C184" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/26T09:03:26+09:00</t>
+        </is>
+      </c>
       <c r="D184" s="22" t="inlineStr">
         <is>
           <t>2027/11/06</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -1918,7 +1918,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>✅ 投稿済み</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>📅 予約済み</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>📅 予約済み</t>
         </is>
       </c>
       <c r="F45" s="19" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>📅 予約済み</t>
         </is>
       </c>
       <c r="F53" s="19" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>📝 予定</t>
+          <t>📅 予約済み</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F194"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9729,7 +9729,114 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="15.75" customHeight="1" s="18"/>
+    <row r="194" ht="15.75" customHeight="1" s="18">
+      <c r="A194" s="26" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="26" t="inlineStr">
+        <is>
+          <t>鼻からの胃カメラ、正直に書くと痛かったです。静岡市の胃がんリスク検診を4,000円で受けてきました</t>
+        </is>
+      </c>
+      <c r="C194" s="26" t="n"/>
+      <c r="D194" s="25" t="inlineStr">
+        <is>
+          <t>2028/01/15</t>
+        </is>
+      </c>
+      <c r="E194" s="26" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F194" s="26" t="inlineStr">
+        <is>
+          <t>数年ぶりに胃カメラを受けてきました🏥
+静岡市の「胃がんリスク検診」という制度を
+使いました。費用は4,000円です。
+そして鼻からの胃カメラは初めてでした。
+先に正直に書きます。
+痛かったです。
+ネットでは「鼻からなら楽」と
+書いてあることが多いのですが
+私はそうではありませんでした。
+【そもそもこの検診を知りませんでした】
+きっかけは近所のクリニックへの問い合わせ。
+「胃カメラを受けたい」と電話したら
+「リスク検診がありますよ」と教えてもらいました。
+自分からはたどり着けていませんでした。
+【静岡市の胃がんリスク検診】
+・令和5年度から
+・35歳〜49歳の期間に、生涯1回だけ
+・ABC検査（血液）＋内視鏡検査のセット
+・費用4,000円（処置が必要なら追加）
+ここが大事です。1回だけです。
+毎年受けるものではなく
+50歳になったら受けられません。
+知らないまま年齢を過ぎてしまう人が
+けっこういるのではないかと思います。
+【申し込みの手順】
+クリニックに行く前に役所への申請が必要でした。
+① クリニックに問い合わせる
+② 自分で役所に連絡して受診券を申請
+③ 受診券が届く
+④ 受診券を持ってクリニックに予約
+②を飛ばすと受けられません。
+【クリニックは「胃カメラが上手」で選びました】
+母親が通院していて
+「あそこは胃カメラが上手」と聞いていたから。
+身内からの口コミは大きかったです。
+【鎮静剤なし、鼻から】
+ゼリー状の麻酔を鼻に注入して10分以上待ちます。
+喉の奥が麻痺してきます。
+体勢によっては呼吸がしにくくなるので
+自分で楽な顔の向きを探していました。
+これは知っておくと違うと思います。
+【正直に書きます。痛かったです】
+鼻の穴が狭いみたいで
+鼻の奥がずっと痛かったです。
+終わったあと鼻血も出ました。
+夜まで血の混じった鼻水や痰が出ていました。
+一方、カメラが胃や十二指腸に入るときは
+痛みではなく「違和感」という感じ。
+鼻 → 痛い
+胃・十二指腸 → 違和感
+という分かれ方でした。
+【自分の胃の中が見られる、はずでした】
+鎮静剤なしなので意識はあります。
+せっかくなので見ようと思っていたら——
+看護師さんがちょうど画面の前に立っていて
+見えませんでした😇
+「見たいです」と先に伝えておくといいかも。
+【時間と、終わったあと】
+全体で1時間程度。
+麻酔が抜けるのは検査後1時間弱。
+胃のムカムカ感が消えず
+お昼はヨーグルトとバナナ程度しか食べられず。
+夜は普通に食べられました。
+当日の昼は軽めのものを用意しておくと安心です。
+【早期発見の差】
+胃がんの5年生存率
+ステージI　92.8%
+ステージII　67.2%
+ステージIII　41.3%
+ステージIV　 6.3%
+ステージIとIVで15倍の開きがあります。
+そして胃がん検診の受診率（2025年）
+男性48.8% / 女性38.3%
+女性のほうが10ポイント低いんです。
+子どもの検診や予防接種には必死になるのに
+自分のことは後回しになりがちですよね。
+私もそうでした。数年ぶりでしたから😅
+※個人の体験です。感じ方には個人差があります。
+※検診の内容や条件は変わることがあります。
+　自治体や医療機関の最新の案内をご確認ください。
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#胃カメラ #内視鏡検査 #胃がんリスク検診 #静岡市 #がん検診 #健康管理 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="195" ht="15.75" customHeight="1" s="18"/>
     <row r="196" ht="15.75" customHeight="1" s="18"/>
     <row r="197" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8888,7 +8888,11 @@
           <t>「紙を見てよー」の一言で済むようになりました。朝のやることリストを貼ってからの経過報告</t>
         </is>
       </c>
-      <c r="C185" s="23" t="n"/>
+      <c r="C185" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/28T09:05:37+09:00</t>
+        </is>
+      </c>
       <c r="D185" s="22" t="inlineStr">
         <is>
           <t>2027/11/13</t>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:F195"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5.25" customWidth="1" style="18" min="1" max="1"/>
@@ -9841,7 +9841,111 @@
         </is>
       </c>
     </row>
-    <row r="195" ht="15.75" customHeight="1" s="18"/>
+    <row r="195" ht="15.75" customHeight="1" s="18">
+      <c r="A195" s="24" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="24" t="inlineStr">
+        <is>
+          <t>「豚肉を油に捧げたんだね」運動会前夜のとんかつと、背中に「輝」と書いて本当に輝いた長女</t>
+        </is>
+      </c>
+      <c r="C195" s="24" t="inlineStr">
+        <is>
+          <t>2026/10/28T20:38:42+09:00</t>
+        </is>
+      </c>
+      <c r="D195" s="25" t="inlineStr">
+        <is>
+          <t>2028/01/22</t>
+        </is>
+      </c>
+      <c r="E195" s="24" t="inlineStr">
+        <is>
+          <t>📝 予定</t>
+        </is>
+      </c>
+      <c r="F195" s="24" t="inlineStr">
+        <is>
+          <t>運動会、無事に終わりました🏃
+雨で延期になったぶん、いいお天気に当たりました。
+まずは前の日の晩ごはんから。
+【3人にリクエストを聞きました】
+長女「パンパーティーでいい」
+長男「とんかつが食べたい」
+次男「何でもいい」
+見事にバラバラですが、全部やりました😂
+・とんかつを家で揚げる
+・フランスパンを購入
+・手作りクリームチーズに鮭の水煮を混ぜてディップ
+このディップが当たりでした。
+ブラックペッパーをかけるとめちゃくちゃ美味しい。
+レリッシュを載せても美味しい。
+長女はクリームチーズと苺ジャムの組み合わせが好きで
+それを頬張っていました。
+長男は「すごく美味しい」と喜んで一言。
+「明日頑張れる！」
+…ちょろいです。でもこういうのでいいんだと思います。
+【そして次男が名言を放ちました】
+「豚肉を油に捧げたんだね」
+笑顔で。
+…捧げた。
+揚げるとは言わず、捧げる。
+しかも悲しそうではなく、にこにこしながら😂
+【当日：長女のダンスとソーラン節】
+CANDY TUNEの「倍倍FIGHT!」はとっても可愛く
+音楽に合わせて首を傾ける感じがもうアイドル。
+そのあとのソーラン節は打って変わってかっこよく
+しっかり腰を下げて踊り切りました。
+そして法被の背中には
+自分で考えた字を絵の具で。
+長女が選んだ字は——「輝」
+まさに輝いていました✨
+よく見ると白い字のまわりに黄色が塗ってあります。
+遠くから見たときに字が浮き上がる配色なんですよね。
+【長男：演技前のエンジンで泣きそうに】
+嵐の「Five」に合わせたフラッグ。
+キビキビと振って、とってもかっこよかったです。
+「横断中」の旗で練習して部品を飛ばした人とは
+思えません。本番では飛びませんでした😇
+演技が始まる前、みんなでエンジンを組んで
+「おー！」
+危うく演技前から泣くところでした。
+家での長男はだらしないです。
+やることリストにいまだに声かけが必要だし
+読書感想文は「今日やる」と言って1週間やらなかった。
+でも今日はシャキッとしていました。
+外ではちゃんとやっている。親が思っているよりずっと。
+組体操では体格がいいので基本的に土台。
+実は今、腕を負傷していて完全な状態ではないのですが
+できる動きはしっかり見せていました。
+みんなで協力したウェーブも綺麗でした。
+【次男：一人だけ縦乗りが激しい】
+M!LKの「爆裂愛してる」。
+家で一度も練習していなかったのに本番も完璧。
+動きも大きく、音楽に合わせてしっかり。
+そして一人だけ、縦乗りが激しい😂
+でもこれが音楽に乗っている感じがしてよかったです。
+【終了式で、また泣きそうに】
+色長さんの感想。
+「運動会は今日1日だけではなく
+　1ヶ月前から頑張ってきたみんなの成果です。
+　支えてくれた先生や保護者に感謝です」
+もう崩壊しそうでした。耐えましたが。
+この言葉が刺さったのは、その1ヶ月を見ていたから。
+鏡の前で何度も踊り直す長女
+「横断中」の旗を振り回して部品を飛ばす長男
+一度も練習せずに突然「俺踊る！」と言い出す次男
+全部ちがうやり方でしたが
+全員が1ヶ月やってきたんですよね。
+本番の数分は、その上に乗っています。
+母は2回泣きそうになって、2回とも耐えました😌
+▶️ 続きはプロフィールのブログへ！
+https://3nin-dotabata.com
+#運動会 #3人育児 #ソーラン節 #小学生ママ #子どもの成長 #子育て日記 #ドタバタ母さん</t>
+        </is>
+      </c>
+    </row>
     <row r="196" ht="15.75" customHeight="1" s="18"/>
     <row r="197" ht="15.75" customHeight="1" s="18"/>
     <row r="198" ht="15.75" customHeight="1" s="18"/>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8253,7 +8253,11 @@
           <t>「どうして俺たちのはないの？」長女に、と思ってもらったカチカチキーホルダーが、結局3人で分けることになった話</t>
         </is>
       </c>
-      <c r="C178" s="23" t="n"/>
+      <c r="C178" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/30T09:07:15+09:00</t>
+        </is>
+      </c>
       <c r="D178" s="22" t="n"/>
       <c r="E178" s="23" t="inlineStr">
         <is>

--- a/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
+++ b/インスタ投稿スケジュール_ドタバタ母さんブログ.xlsx
@@ -8437,7 +8437,11 @@
           <t>「姿勢よく食べよう」と言い続けても直らなかった次男。椅子を変えたら、その日から一度も膝を立てませんでした</t>
         </is>
       </c>
-      <c r="C180" s="23" t="n"/>
+      <c r="C180" s="23" t="inlineStr">
+        <is>
+          <t>2026/10/31T09:07:23+09:00</t>
+        </is>
+      </c>
       <c r="D180" s="22" t="inlineStr">
         <is>
           <t>2027/10/09</t>
